--- a/25-새서울철도-서초구-보고서.xlsx
+++ b/25-새서울철도-서초구-보고서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1961D81-D6D1-4768-8658-E976FFB378D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE986E2-90E9-40A1-8C04-B0A8E8A99387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22824" yWindow="48" windowWidth="23256" windowHeight="12972" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="146">
   <si>
     <t>시행년도</t>
   </si>
@@ -3211,6 +3211,142 @@
     <t>지번 주소
 (도로명 주소)</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 12-17</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>신사역교차로</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 20-5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 21-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 21-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 21-7</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 27-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 27-8</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 28-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 28-10</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 28-6</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 36-14</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠원동 37-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현역교차로</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 707-11</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 706-10</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 707-5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 722-20</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 723-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 736-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>반포동 736-17</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1303-43</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1303-22</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1303-35</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1304-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1304-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1305</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1305-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1305-7</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1306</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1306-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1306-8</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1318</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초동 1318-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3363,18 +3499,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3457,6 +3581,18 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4463,13 +4599,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:rowOff>41638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2901043</xdr:colOff>
+      <xdr:colOff>2899138</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>1642382</xdr:rowOff>
     </xdr:to>
@@ -4501,8 +4637,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="26985686"/>
-          <a:ext cx="2724150" cy="1598839"/>
+          <a:off x="13687969" y="26951124"/>
+          <a:ext cx="2720340" cy="1600744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4768,13 +4904,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:rowOff>41638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2901043</xdr:colOff>
+      <xdr:colOff>2899138</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>1642382</xdr:rowOff>
     </xdr:to>
@@ -4806,8 +4942,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="35218007"/>
-          <a:ext cx="2724150" cy="1598839"/>
+          <a:off x="13687969" y="35169838"/>
+          <a:ext cx="2720340" cy="1600744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4829,9 +4965,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>43542</xdr:rowOff>
+      <xdr:rowOff>41637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
@@ -4867,8 +5003,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="36864471"/>
-          <a:ext cx="2714625" cy="1598840"/>
+          <a:off x="13687969" y="36813580"/>
+          <a:ext cx="2712720" cy="1600745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5012,9 +5148,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:rowOff>41638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
@@ -5050,8 +5186,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="41803864"/>
-          <a:ext cx="2714625" cy="1598839"/>
+          <a:off x="13687969" y="41744809"/>
+          <a:ext cx="2712720" cy="1600744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5195,9 +5331,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:rowOff>41638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
@@ -5233,8 +5369,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="46743257"/>
-          <a:ext cx="2714625" cy="1598839"/>
+          <a:off x="13687969" y="46676038"/>
+          <a:ext cx="2712720" cy="1600744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5256,9 +5392,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>43542</xdr:rowOff>
+      <xdr:rowOff>41637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
@@ -5294,8 +5430,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="48389721"/>
-          <a:ext cx="2714625" cy="1598840"/>
+          <a:off x="13687969" y="48319780"/>
+          <a:ext cx="2712720" cy="1600745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5500,13 +5636,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>161381</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>43542</xdr:rowOff>
+      <xdr:rowOff>41637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2877911</xdr:colOff>
+      <xdr:colOff>2881721</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>1642382</xdr:rowOff>
     </xdr:to>
@@ -5538,8 +5674,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579929" y="54975578"/>
-          <a:ext cx="2714625" cy="1598840"/>
+          <a:off x="13670552" y="54894751"/>
+          <a:ext cx="2720340" cy="1600745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5683,15 +5819,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163285</xdr:colOff>
+      <xdr:colOff>161380</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>29935</xdr:rowOff>
+      <xdr:rowOff>31840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2887435</xdr:colOff>
+      <xdr:colOff>2889340</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>1628775</xdr:rowOff>
+      <xdr:rowOff>1630680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5721,8 +5857,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579928" y="59901364"/>
-          <a:ext cx="2724150" cy="1598840"/>
+          <a:off x="13670551" y="59816183"/>
+          <a:ext cx="2727960" cy="1598840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5805,15 +5941,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163285</xdr:colOff>
+      <xdr:colOff>161380</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>29936</xdr:rowOff>
+      <xdr:rowOff>31841</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2877910</xdr:colOff>
+      <xdr:colOff>2881720</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>1628775</xdr:rowOff>
+      <xdr:rowOff>1630680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5843,8 +5979,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579928" y="63194293"/>
-          <a:ext cx="2714625" cy="1598839"/>
+          <a:off x="13670551" y="63103670"/>
+          <a:ext cx="2720340" cy="1598839"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8612,2657 +8748,2737 @@
   <dimension ref="A1:T47"/>
   <sheetFormatPr defaultColWidth="10.375" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="17" width="10.375" style="5"/>
-    <col min="18" max="18" width="39.125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="10.375" style="6"/>
-    <col min="20" max="16384" width="10.375" style="5"/>
+    <col min="1" max="17" width="10.375" style="1"/>
+    <col min="18" max="18" width="39.125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.375" style="2"/>
+    <col min="20" max="16384" width="10.375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="12" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="12" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>2025</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="12" customHeight="1"/>
     <row r="4" spans="1:20" ht="12" customHeight="1"/>
     <row r="5" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="R5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="T5" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="4">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="4" t="str">
         <f t="shared" ref="C6:C45" si="0">RIGHT($A$2,2)&amp;"-"&amp;$C$2&amp;"-"&amp;A6</f>
         <v>25-서초구-1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="6">
         <v>2</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="6">
         <f t="shared" ref="I6:I45" si="1">IF(D6="양호",0,IF(D6="보통",3,IF(D6="긴급",9)))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="6">
         <f t="shared" ref="J6:J45" si="2">IF(E6="거북등",3,IF(RIGHT(E6,2)="균열",1,IF(E6="-",0)))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="6">
         <f t="shared" ref="K6:K45" si="3">IF(F6="유출",9,IF(F6="습윤",1,IF(F6="양호",0,IF(F6="건조",0))))</f>
         <v>0</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="6">
         <f t="shared" ref="L6:L45" si="4">IF(G6&lt;10,0,IF(G6&lt;30,1,IF(G6&gt;=30,2)))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="6">
         <f t="shared" ref="M6:M45" si="5">IF(H6="-",0,1)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="6">
         <f t="shared" ref="N6:N45" si="6">SUM(I6:M6)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="10" t="str">
+      <c r="O6" s="6" t="str">
         <f t="shared" ref="O6:O45" si="7">IF(N6&lt;6,"일반",IF(N6&lt;9,"우선",IF(N6&gt;=9,"긴급")))</f>
         <v>일반</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="11" t="s">
+      <c r="Q6" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="R6" s="29"/>
+      <c r="S6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="T6" s="12"/>
+      <c r="T6" s="8"/>
     </row>
     <row r="7" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A7" s="10">
+      <c r="A7" s="6">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="10" t="str">
+      <c r="C7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-2</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="6">
         <v>2</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O7" s="10" t="str">
+      <c r="O7" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="11" t="s">
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="R7" s="29"/>
+      <c r="S7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="T7" s="12"/>
+      <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A8" s="10">
+      <c r="A8" s="6">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="10" t="str">
+      <c r="C8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="6">
         <v>2</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="6">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="O8" s="10" t="str">
+      <c r="O8" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="11" t="s">
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R8" s="29"/>
+      <c r="S8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="T8" s="12"/>
+      <c r="T8" s="8"/>
     </row>
     <row r="9" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A9" s="10">
+      <c r="A9" s="6">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10" t="str">
+      <c r="C9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="6">
         <v>2</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O9" s="10" t="str">
+      <c r="O9" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="13" t="s">
+      <c r="Q9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="29"/>
+      <c r="S9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="T9" s="12"/>
+      <c r="T9" s="8"/>
     </row>
     <row r="10" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A10" s="10">
+      <c r="A10" s="6">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="10" t="str">
+      <c r="C10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-5</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="6">
         <v>2</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O10" s="10" t="str">
+      <c r="O10" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="13" t="s">
+      <c r="Q10" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="R10" s="29"/>
+      <c r="S10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="12"/>
+      <c r="T10" s="8"/>
     </row>
     <row r="11" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A11" s="10">
+      <c r="A11" s="6">
         <v>6</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="10" t="str">
+      <c r="C11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-6</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="6">
         <v>2</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O11" s="10" t="str">
+      <c r="O11" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="11" t="s">
+      <c r="Q11" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="R11" s="29"/>
+      <c r="S11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="T11" s="12"/>
+      <c r="T11" s="8"/>
     </row>
     <row r="12" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A12" s="10">
+      <c r="A12" s="6">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="10" t="str">
+      <c r="C12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-7</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="6">
         <v>2</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O12" s="10" t="str">
+      <c r="O12" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="11" t="s">
+      <c r="Q12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="R12" s="29"/>
+      <c r="S12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="T12" s="12"/>
+      <c r="T12" s="8"/>
     </row>
     <row r="13" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="6">
         <v>8</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="10" t="str">
+      <c r="C13" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-8</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="6">
         <v>2</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O13" s="10" t="str">
+      <c r="O13" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="11" t="s">
+      <c r="Q13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="R13" s="29"/>
+      <c r="S13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="T13" s="12"/>
+      <c r="T13" s="8"/>
     </row>
     <row r="14" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="6">
         <v>9</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="10" t="str">
+      <c r="C14" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-9</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="6">
         <v>2</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O14" s="10" t="str">
+      <c r="O14" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P14" s="10" t="s">
+      <c r="P14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="11" t="s">
+      <c r="Q14" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R14" s="29"/>
+      <c r="S14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="T14" s="12"/>
+      <c r="T14" s="8"/>
     </row>
     <row r="15" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="6">
         <v>10</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="10" t="str">
+      <c r="C15" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-10</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="6">
         <v>2</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O15" s="10" t="str">
+      <c r="O15" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="11" t="s">
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="R15" s="29"/>
+      <c r="S15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="T15" s="12"/>
+      <c r="T15" s="8"/>
     </row>
     <row r="16" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="6">
         <v>11</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="10" t="str">
+      <c r="C16" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-11</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="6">
         <v>2</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O16" s="10" t="str">
+      <c r="O16" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="11" t="s">
+      <c r="Q16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="R16" s="29"/>
+      <c r="S16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T16" s="12"/>
+      <c r="T16" s="8"/>
     </row>
     <row r="17" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="6">
         <v>12</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="10" t="str">
+      <c r="C17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-12</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="6">
         <v>2</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O17" s="10" t="str">
+      <c r="O17" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="P17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="13" t="s">
+      <c r="Q17" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" s="29"/>
+      <c r="S17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="T17" s="12"/>
+      <c r="T17" s="8"/>
     </row>
     <row r="18" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="6">
         <v>13</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10" t="str">
+      <c r="C18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-13</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="6">
         <v>2</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O18" s="10" t="str">
+      <c r="O18" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="P18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="11" t="s">
+      <c r="Q18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="R18" s="29"/>
+      <c r="S18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="T18" s="12"/>
+      <c r="T18" s="8"/>
     </row>
     <row r="19" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="6">
         <v>14</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="10" t="str">
+      <c r="C19" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-14</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="6">
         <v>2</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O19" s="10" t="str">
+      <c r="O19" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P19" s="8" t="s">
+      <c r="P19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="11" t="s">
+      <c r="Q19" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="R19" s="29"/>
+      <c r="S19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="T19" s="12"/>
+      <c r="T19" s="8"/>
     </row>
     <row r="20" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A20" s="10">
+      <c r="A20" s="6">
         <v>15</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="10" t="str">
+      <c r="C20" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-15</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="6">
         <v>2</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O20" s="10" t="str">
+      <c r="O20" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="13" t="s">
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="R20" s="29"/>
+      <c r="S20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="T20" s="12"/>
+      <c r="T20" s="8"/>
     </row>
     <row r="21" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A21" s="10">
+      <c r="A21" s="6">
         <v>16</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="10" t="str">
+      <c r="C21" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-16</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="6">
         <v>2</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O21" s="10" t="str">
+      <c r="O21" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="13" t="s">
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="R21" s="29"/>
+      <c r="S21" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="T21" s="8"/>
     </row>
     <row r="22" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A22" s="10">
+      <c r="A22" s="6">
         <v>17</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="10" t="str">
+      <c r="C22" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-17</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="6">
         <v>2</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O22" s="10" t="str">
+      <c r="O22" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P22" s="10" t="s">
+      <c r="P22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="11" t="s">
+      <c r="Q22" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="R22" s="29"/>
+      <c r="S22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T22" s="12"/>
+      <c r="T22" s="8"/>
     </row>
     <row r="23" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A23" s="10">
+      <c r="A23" s="6">
         <v>18</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="10" t="str">
+      <c r="C23" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-18</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="6">
         <v>2</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O23" s="10" t="str">
+      <c r="O23" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="11" t="s">
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="R23" s="29"/>
+      <c r="S23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="T23" s="12"/>
+      <c r="T23" s="8"/>
     </row>
     <row r="24" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A24" s="10">
+      <c r="A24" s="6">
         <v>19</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="10" t="str">
+      <c r="C24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-19</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="6">
         <v>2</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O24" s="10" t="str">
+      <c r="O24" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="11" t="s">
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="29"/>
+      <c r="S24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="T24" s="12"/>
+      <c r="T24" s="8"/>
     </row>
     <row r="25" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A25" s="10">
+      <c r="A25" s="6">
         <v>20</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="10" t="str">
+      <c r="C25" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-20</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="6">
         <v>2</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="6">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="O25" s="10" t="str">
+      <c r="O25" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="11" t="s">
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="R25" s="29"/>
+      <c r="S25" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="T25" s="12"/>
+      <c r="T25" s="8"/>
     </row>
     <row r="26" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A26" s="10">
+      <c r="A26" s="6">
         <v>21</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="10" t="str">
+      <c r="C26" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-21</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="6">
         <v>2</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O26" s="10" t="str">
+      <c r="O26" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="11" t="s">
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="R26" s="29"/>
+      <c r="S26" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="T26" s="12"/>
+      <c r="T26" s="8"/>
     </row>
     <row r="27" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A27" s="10">
+      <c r="A27" s="6">
         <v>22</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="10" t="str">
+      <c r="C27" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-22</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="6">
         <v>2</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O27" s="10" t="str">
+      <c r="O27" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="11" t="s">
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="R27" s="29"/>
+      <c r="S27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="T27" s="12"/>
+      <c r="T27" s="8"/>
     </row>
     <row r="28" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A28" s="10">
+      <c r="A28" s="6">
         <v>23</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="10" t="str">
+      <c r="C28" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-23</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="6">
         <v>2</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O28" s="10" t="str">
+      <c r="O28" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P28" s="8" t="s">
+      <c r="P28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="11" t="s">
+      <c r="Q28" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="R28" s="29"/>
+      <c r="S28" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="T28" s="12"/>
+      <c r="T28" s="8"/>
     </row>
     <row r="29" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A29" s="10">
+      <c r="A29" s="6">
         <v>24</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="10" t="str">
+      <c r="C29" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-24</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="6">
         <v>2</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O29" s="10" t="str">
+      <c r="O29" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="11" t="s">
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="R29" s="29"/>
+      <c r="S29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="T29" s="12"/>
+      <c r="T29" s="8"/>
     </row>
     <row r="30" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A30" s="10">
+      <c r="A30" s="6">
         <v>25</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="10" t="str">
+      <c r="C30" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-25</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="6">
         <v>2</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O30" s="10" t="str">
+      <c r="O30" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="11" t="s">
+      <c r="P30" s="6"/>
+      <c r="Q30" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="R30" s="29"/>
+      <c r="S30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="T30" s="12"/>
+      <c r="T30" s="8"/>
     </row>
     <row r="31" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A31" s="10">
+      <c r="A31" s="6">
         <v>26</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="10" t="str">
+      <c r="C31" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-26</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="6">
         <v>2</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O31" s="10" t="str">
+      <c r="O31" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="11" t="s">
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R31" s="29"/>
+      <c r="S31" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="T31" s="12"/>
+      <c r="T31" s="8"/>
     </row>
     <row r="32" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A32" s="10">
+      <c r="A32" s="6">
         <v>27</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="10" t="str">
+      <c r="C32" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-27</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="6">
         <v>2</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M32" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="6">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="O32" s="10" t="str">
+      <c r="O32" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="11" t="s">
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="29"/>
+      <c r="S32" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="T32" s="12"/>
+      <c r="T32" s="8"/>
     </row>
     <row r="33" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A33" s="10">
+      <c r="A33" s="6">
         <v>28</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="10" t="str">
+      <c r="C33" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-28</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="6">
         <v>2</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O33" s="10" t="str">
+      <c r="O33" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="11" t="s">
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="R33" s="29"/>
+      <c r="S33" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="T33" s="12"/>
+      <c r="T33" s="8"/>
     </row>
     <row r="34" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A34" s="10">
+      <c r="A34" s="6">
         <v>29</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="10" t="str">
+      <c r="C34" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-29</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="6">
         <v>2</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M34" s="10">
+      <c r="M34" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O34" s="10" t="str">
+      <c r="O34" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="11" t="s">
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="R34" s="29"/>
+      <c r="S34" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="T34" s="12"/>
+      <c r="T34" s="8"/>
     </row>
     <row r="35" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A35" s="10">
+      <c r="A35" s="6">
         <v>30</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="10" t="str">
+      <c r="C35" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-30</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="6">
         <v>2</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M35" s="10">
+      <c r="M35" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O35" s="10" t="str">
+      <c r="O35" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P35" s="10" t="s">
+      <c r="P35" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="11" t="s">
+      <c r="Q35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="R35" s="29"/>
+      <c r="S35" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="T35" s="12"/>
+      <c r="T35" s="8"/>
     </row>
     <row r="36" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A36" s="10">
+      <c r="A36" s="6">
         <v>31</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="10" t="str">
+      <c r="C36" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-31</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="6">
         <v>2</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I36" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J36" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M36" s="10">
+      <c r="M36" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O36" s="10" t="str">
+      <c r="O36" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P36" s="10" t="s">
+      <c r="P36" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="11" t="s">
+      <c r="Q36" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R36" s="29"/>
+      <c r="S36" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="T36" s="12"/>
+      <c r="T36" s="8"/>
     </row>
     <row r="37" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A37" s="10">
+      <c r="A37" s="6">
         <v>32</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="10" t="str">
+      <c r="C37" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-32</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="6">
         <v>2</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="14" t="b">
+      <c r="K37" s="10" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M37" s="10">
+      <c r="M37" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N37" s="10">
+      <c r="N37" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O37" s="10" t="str">
+      <c r="O37" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P37" s="8" t="s">
+      <c r="P37" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="11" t="s">
+      <c r="Q37" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="R37" s="29"/>
+      <c r="S37" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="T37" s="12"/>
+      <c r="T37" s="8"/>
     </row>
     <row r="38" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A38" s="10">
+      <c r="A38" s="6">
         <v>33</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="10" t="str">
+      <c r="C38" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-33</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="6">
         <v>2</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M38" s="10">
+      <c r="M38" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O38" s="10" t="str">
+      <c r="O38" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="11" t="s">
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="R38" s="29"/>
+      <c r="S38" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="T38" s="12"/>
+      <c r="T38" s="8"/>
     </row>
     <row r="39" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A39" s="10">
+      <c r="A39" s="6">
         <v>34</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="10" t="str">
+      <c r="C39" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-34</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="6">
         <v>2</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M39" s="10">
+      <c r="M39" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O39" s="10" t="str">
+      <c r="O39" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="11" t="s">
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="R39" s="29"/>
+      <c r="S39" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="T39" s="12"/>
+      <c r="T39" s="8"/>
     </row>
     <row r="40" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A40" s="10">
+      <c r="A40" s="6">
         <v>35</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="10" t="str">
+      <c r="C40" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-35</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="6">
         <v>2</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I40" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J40" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M40" s="10">
+      <c r="M40" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N40" s="10">
+      <c r="N40" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O40" s="10" t="str">
+      <c r="O40" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="11" t="s">
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="R40" s="29"/>
+      <c r="S40" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="T40" s="12"/>
+      <c r="T40" s="8"/>
     </row>
     <row r="41" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A41" s="10">
+      <c r="A41" s="6">
         <v>36</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="10" t="str">
+      <c r="C41" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-36</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="6">
         <v>2</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I41" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M41" s="10">
+      <c r="M41" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N41" s="10">
+      <c r="N41" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O41" s="10" t="str">
+      <c r="O41" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="13" t="s">
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R41" s="29"/>
+      <c r="S41" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="T41" s="12"/>
+      <c r="T41" s="8"/>
     </row>
     <row r="42" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A42" s="10">
+      <c r="A42" s="6">
         <v>37</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="10" t="str">
+      <c r="C42" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-37</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="6">
         <v>2</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O42" s="10" t="str">
+      <c r="O42" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="11" t="s">
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="R42" s="29"/>
+      <c r="S42" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="T42" s="12"/>
+      <c r="T42" s="8"/>
     </row>
     <row r="43" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A43" s="10">
+      <c r="A43" s="6">
         <v>38</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="10" t="str">
+      <c r="C43" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-38</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="6">
         <v>2</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M43" s="10">
+      <c r="M43" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O43" s="10" t="str">
+      <c r="O43" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P43" s="10" t="s">
+      <c r="P43" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="11" t="s">
+      <c r="Q43" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="R43" s="29"/>
+      <c r="S43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="T43" s="12"/>
+      <c r="T43" s="8"/>
     </row>
     <row r="44" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A44" s="10">
+      <c r="A44" s="6">
         <v>39</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="10" t="str">
+      <c r="C44" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-39</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="6">
         <v>2</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I44" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J44" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M44" s="10">
+      <c r="M44" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N44" s="10">
+      <c r="N44" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O44" s="10" t="str">
+      <c r="O44" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="11" t="s">
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="R44" s="29"/>
+      <c r="S44" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="T44" s="12"/>
+      <c r="T44" s="8"/>
     </row>
     <row r="45" spans="1:20" ht="129.75" customHeight="1">
-      <c r="A45" s="10">
+      <c r="A45" s="6">
         <v>40</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="10" t="str">
+      <c r="C45" s="6" t="str">
         <f t="shared" si="0"/>
         <v>25-서초구-40</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="6">
         <v>2</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I45" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="6">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="O45" s="10" t="str">
+      <c r="O45" s="6" t="str">
         <f t="shared" si="7"/>
         <v>일반</v>
       </c>
-      <c r="P45" s="10" t="s">
+      <c r="P45" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="11" t="s">
+      <c r="Q45" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="R45" s="29"/>
+      <c r="S45" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="T45" s="12"/>
+      <c r="T45" s="8"/>
     </row>
     <row r="46" spans="1:20">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="12"/>
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="8"/>
     </row>
     <row r="47" spans="1:20">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="12"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -11277,36 +11493,36 @@
   <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="39.125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="25.375" style="16" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="11" customWidth="1"/>
+    <col min="2" max="2" width="39.125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="25.375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="6.75" customHeight="1"/>
     <row r="4" spans="1:3" ht="33">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="27" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A5" s="18" t="str">
+      <c r="A5" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A6</f>
         <v>25-서초구-1</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="19" t="str">
+      <c r="B5" s="29"/>
+      <c r="C5" s="15" t="str">
         <f>IF(RawData!S6="","-",RawData!S6)</f>
         <v>피난계단 옆(상선)
 보도
@@ -11314,12 +11530,12 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A6" s="18" t="str">
+      <c r="A6" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A7</f>
         <v>25-서초구-2</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="19" t="str">
+      <c r="B6" s="29"/>
+      <c r="C6" s="15" t="str">
         <f>IF(RawData!S7="","-",RawData!S7)</f>
         <v>신사역 교차로
 도로
@@ -11327,12 +11543,12 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A7" s="18" t="str">
+      <c r="A7" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A8</f>
         <v>25-서초구-3</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="19" t="str">
+      <c r="B7" s="29"/>
+      <c r="C7" s="15" t="str">
         <f>IF(RawData!S8="","-",RawData!S8)</f>
         <v>파리바게트 앞
 도로
@@ -11340,12 +11556,12 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A8" s="18" t="str">
+      <c r="A8" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A9</f>
         <v>25-서초구-4</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="19" t="str">
+      <c r="B8" s="29"/>
+      <c r="C8" s="15" t="str">
         <f>IF(RawData!S9="","-",RawData!S9)</f>
         <v>CELL TRION 앞
 도로
@@ -11353,12 +11569,12 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A9" s="18" t="str">
+      <c r="A9" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A10</f>
         <v>25-서초구-5</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="19" t="str">
+      <c r="B9" s="29"/>
+      <c r="C9" s="15" t="str">
         <f>IF(RawData!S10="","-",RawData!S10)</f>
         <v>CELL TRION 앞
 보도
@@ -11366,12 +11582,12 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A10" s="18" t="str">
+      <c r="A10" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A11</f>
         <v>25-서초구-6</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="19" t="str">
+      <c r="B10" s="29"/>
+      <c r="C10" s="15" t="str">
         <f>IF(RawData!S11="","-",RawData!S11)</f>
         <v>서울미소그린치과 앞
 버스정류장
@@ -11380,12 +11596,12 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A11" s="18" t="str">
+      <c r="A11" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A12</f>
         <v>25-서초구-7</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="19" t="str">
+      <c r="B11" s="29"/>
+      <c r="C11" s="15" t="str">
         <f>IF(RawData!S12="","-",RawData!S12)</f>
         <v>씨티약국 앞
 도로
@@ -11393,12 +11609,12 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A12" s="18" t="str">
+      <c r="A12" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A13</f>
         <v>25-서초구-8</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="19" t="str">
+      <c r="B12" s="29"/>
+      <c r="C12" s="15" t="str">
         <f>IF(RawData!S13="","-",RawData!S13)</f>
         <v>스타벅스 앞
 버스차선
@@ -11406,12 +11622,12 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A13" s="18" t="str">
+      <c r="A13" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A14</f>
         <v>25-서초구-9</v>
       </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="19" t="str">
+      <c r="B13" s="29"/>
+      <c r="C13" s="15" t="str">
         <f>IF(RawData!S14="","-",RawData!S14)</f>
         <v>이디아커피 앞
 도로
@@ -11419,12 +11635,12 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A14" s="18" t="str">
+      <c r="A14" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A15</f>
         <v>25-서초구-10</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="19" t="str">
+      <c r="B14" s="29"/>
+      <c r="C14" s="15" t="str">
         <f>IF(RawData!S15="","-",RawData!S15)</f>
         <v>하나은행 앞
 도로
@@ -11432,12 +11648,12 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A15" s="18" t="str">
+      <c r="A15" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A16</f>
         <v>25-서초구-11</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="19" t="str">
+      <c r="B15" s="29"/>
+      <c r="C15" s="15" t="str">
         <f>IF(RawData!S16="","-",RawData!S16)</f>
         <v>페페신사 앞
 도로
@@ -11445,12 +11661,12 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A16" s="18" t="str">
+      <c r="A16" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A17</f>
         <v>25-서초구-12</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="19" t="str">
+      <c r="B16" s="29"/>
+      <c r="C16" s="15" t="str">
         <f>IF(RawData!S17="","-",RawData!S17)</f>
         <v>HY빌딩 앞
 도로
@@ -11458,12 +11674,12 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A17" s="18" t="str">
+      <c r="A17" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A18</f>
         <v>25-서초구-13</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="19" t="str">
+      <c r="B17" s="29"/>
+      <c r="C17" s="15" t="str">
         <f>IF(RawData!S18="","-",RawData!S18)</f>
         <v>현장(잠원동28-6) 앞
 도로
@@ -11471,12 +11687,12 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A18" s="18" t="str">
+      <c r="A18" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A19</f>
         <v>25-서초구-14</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="19" t="str">
+      <c r="B18" s="29"/>
+      <c r="C18" s="15" t="str">
         <f>IF(RawData!S19="","-",RawData!S19)</f>
         <v>현장(잠원동28-6) 앞
 보도
@@ -11484,12 +11700,12 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A19" s="18" t="str">
+      <c r="A19" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A20</f>
         <v>25-서초구-15</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="19" t="str">
+      <c r="B19" s="29"/>
+      <c r="C19" s="15" t="str">
         <f>IF(RawData!S20="","-",RawData!S20)</f>
         <v>KDB산업은행 앞
 도로
@@ -11497,12 +11713,12 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A20" s="18" t="str">
+      <c r="A20" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A21</f>
         <v>25-서초구-16</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="19" t="str">
+      <c r="B20" s="29"/>
+      <c r="C20" s="15" t="str">
         <f>IF(RawData!S21="","-",RawData!S21)</f>
         <v>ok광생약국 앞
 도로
@@ -11510,24 +11726,24 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A21" s="18" t="str">
+      <c r="A21" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A22</f>
         <v>25-서초구-17</v>
       </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="19" t="str">
+      <c r="B21" s="29"/>
+      <c r="C21" s="15" t="str">
         <f>IF(RawData!S22="","-",RawData!S22)</f>
         <v>논현역 교차로
 (강남대로)</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A22" s="18" t="str">
+      <c r="A22" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A23</f>
         <v>25-서초구-18</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="19" t="str">
+      <c r="B22" s="29"/>
+      <c r="C22" s="15" t="str">
         <f>IF(RawData!S23="","-",RawData!S23)</f>
         <v>논현역 #5번출 앞
 도로
@@ -11535,12 +11751,12 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A23" s="18" t="str">
+      <c r="A23" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A24</f>
         <v>25-서초구-19</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="19" t="str">
+      <c r="B23" s="29"/>
+      <c r="C23" s="15" t="str">
         <f>IF(RawData!S24="","-",RawData!S24)</f>
         <v>논현역 E/V_2호기 앞
 도로
@@ -11548,12 +11764,12 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A24" s="18" t="str">
+      <c r="A24" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A25</f>
         <v>25-서초구-20</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="19" t="str">
+      <c r="B24" s="29"/>
+      <c r="C24" s="15" t="str">
         <f>IF(RawData!S25="","-",RawData!S25)</f>
         <v>논현역 #4번출구 앞
 도로
@@ -11561,12 +11777,12 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A25" s="18" t="str">
+      <c r="A25" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A26</f>
         <v>25-서초구-21</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="19" t="str">
+      <c r="B25" s="29"/>
+      <c r="C25" s="15" t="str">
         <f>IF(RawData!S26="","-",RawData!S26)</f>
         <v>참치 앤 쿡 앞
 도로
@@ -11574,12 +11790,12 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A26" s="18" t="str">
+      <c r="A26" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A27</f>
         <v>25-서초구-22</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="19" t="str">
+      <c r="B26" s="29"/>
+      <c r="C26" s="15" t="str">
         <f>IF(RawData!S27="","-",RawData!S27)</f>
         <v>뮬리성형외과 앞
 도로
@@ -11587,12 +11803,12 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A27" s="18" t="str">
+      <c r="A27" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A28</f>
         <v>25-서초구-23</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="19" t="str">
+      <c r="B27" s="29"/>
+      <c r="C27" s="15" t="str">
         <f>IF(RawData!S28="","-",RawData!S28)</f>
         <v>강남성모원 안과의원 앞
 보도
@@ -11600,12 +11816,12 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A28" s="18" t="str">
+      <c r="A28" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A29</f>
         <v>25-서초구-24</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="19" t="str">
+      <c r="B28" s="29"/>
+      <c r="C28" s="15" t="str">
         <f>IF(RawData!S29="","-",RawData!S29)</f>
         <v>커피빈 앞
 도로
@@ -11613,12 +11829,12 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A29" s="18" t="str">
+      <c r="A29" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A30</f>
         <v>25-서초구-25</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="19" t="str">
+      <c r="B29" s="29"/>
+      <c r="C29" s="15" t="str">
         <f>IF(RawData!S30="","-",RawData!S30)</f>
         <v>스타벅스 앞
 도로
@@ -11626,12 +11842,12 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A30" s="18" t="str">
+      <c r="A30" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A31</f>
         <v>25-서초구-26</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="19" t="str">
+      <c r="B30" s="29"/>
+      <c r="C30" s="15" t="str">
         <f>IF(RawData!S31="","-",RawData!S31)</f>
         <v>신논현역 교차로
 =교보타워 교차로
@@ -11639,12 +11855,12 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A31" s="18" t="str">
+      <c r="A31" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A32</f>
         <v>25-서초구-27</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="19" t="str">
+      <c r="B31" s="29"/>
+      <c r="C31" s="15" t="str">
         <f>IF(RawData!S32="","-",RawData!S32)</f>
         <v>교보타워 주차장 앞
 도로
@@ -11652,12 +11868,12 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A32" s="18" t="str">
+      <c r="A32" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A33</f>
         <v>25-서초구-28</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="19" t="str">
+      <c r="B32" s="29"/>
+      <c r="C32" s="15" t="str">
         <f>IF(RawData!S33="","-",RawData!S33)</f>
         <v>던킹도너츠 앞
 도로
@@ -11665,12 +11881,12 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A33" s="18" t="str">
+      <c r="A33" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A34</f>
         <v>25-서초구-29</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="19" t="str">
+      <c r="B33" s="29"/>
+      <c r="C33" s="15" t="str">
         <f>IF(RawData!S34="","-",RawData!S34)</f>
         <v>수세연 안과의원
 도로
@@ -11678,12 +11894,12 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A34" s="18" t="str">
+      <c r="A34" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A35</f>
         <v>25-서초구-30</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="19" t="str">
+      <c r="B34" s="29"/>
+      <c r="C34" s="15" t="str">
         <f>IF(RawData!S35="","-",RawData!S35)</f>
         <v>자라 앞
 도로
@@ -11691,12 +11907,12 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A35" s="18" t="str">
+      <c r="A35" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A36</f>
         <v>25-서초구-31</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="19" t="str">
+      <c r="B35" s="29"/>
+      <c r="C35" s="15" t="str">
         <f>IF(RawData!S36="","-",RawData!S36)</f>
         <v>준오헤어 앞
 보도
@@ -11704,12 +11920,12 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A36" s="18" t="str">
+      <c r="A36" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A37</f>
         <v>25-서초구-32</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="19" t="str">
+      <c r="B36" s="29"/>
+      <c r="C36" s="15" t="str">
         <f>IF(RawData!S37="","-",RawData!S37)</f>
         <v>준오헤어 앞
 도로
@@ -11717,12 +11933,12 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A37" s="18" t="str">
+      <c r="A37" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A38</f>
         <v>25-서초구-33</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="19" t="str">
+      <c r="B37" s="29"/>
+      <c r="C37" s="15" t="str">
         <f>IF(RawData!S38="","-",RawData!S38)</f>
         <v>라인프렌즈 앞
 도로
@@ -11730,12 +11946,12 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A38" s="18" t="str">
+      <c r="A38" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A39</f>
         <v>25-서초구-34</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="19" t="str">
+      <c r="B38" s="29"/>
+      <c r="C38" s="15" t="str">
         <f>IF(RawData!S39="","-",RawData!S39)</f>
         <v>올리브영 앞
 도로
@@ -11743,12 +11959,12 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A39" s="18" t="str">
+      <c r="A39" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A40</f>
         <v>25-서초구-35</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="19" t="str">
+      <c r="B39" s="29"/>
+      <c r="C39" s="15" t="str">
         <f>IF(RawData!S40="","-",RawData!S40)</f>
         <v>비엠사오 앞
 도로
@@ -11756,12 +11972,12 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A40" s="18" t="str">
+      <c r="A40" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A41</f>
         <v>25-서초구-36</v>
       </c>
-      <c r="B40" s="33"/>
-      <c r="C40" s="19" t="str">
+      <c r="B40" s="29"/>
+      <c r="C40" s="15" t="str">
         <f>IF(RawData!S41="","-",RawData!S41)</f>
         <v>ABC마트 앞
 도로
@@ -11769,12 +11985,12 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A41" s="18" t="str">
+      <c r="A41" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A42</f>
         <v>25-서초구-37</v>
       </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="19" t="str">
+      <c r="B41" s="29"/>
+      <c r="C41" s="15" t="str">
         <f>IF(RawData!S42="","-",RawData!S42)</f>
         <v>강남 성모안과 앞
 도로
@@ -11782,12 +11998,12 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A42" s="18" t="str">
+      <c r="A42" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A43</f>
         <v>25-서초구-38</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="19" t="str">
+      <c r="B42" s="29"/>
+      <c r="C42" s="15" t="str">
         <f>IF(RawData!S43="","-",RawData!S43)</f>
         <v>강남 성모안과 앞
 횡단보도
@@ -11795,12 +12011,12 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A43" s="18" t="str">
+      <c r="A43" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A44</f>
         <v>25-서초구-39</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="19" t="str">
+      <c r="B43" s="29"/>
+      <c r="C43" s="15" t="str">
         <f>IF(RawData!S44="","-",RawData!S44)</f>
         <v>삼성스토어 앞
 도로
@@ -11808,12 +12024,12 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="129.75" customHeight="1">
-      <c r="A44" s="18" t="str">
+      <c r="A44" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A45</f>
         <v>25-서초구-40</v>
       </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="19" t="str">
+      <c r="B44" s="29"/>
+      <c r="C44" s="15" t="str">
         <f>IF(RawData!S45="","-",RawData!S45)</f>
         <v>하나은행 앞
 도로
@@ -11821,19 +12037,19 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="18"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="19"/>
+      <c r="A45" s="14"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="15"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="18"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="19"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="15"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="20"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -11851,2839 +12067,2839 @@
   <dimension ref="A2:S50"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="11.625" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="15" customWidth="1"/>
-    <col min="14" max="15" width="4.375" style="15" customWidth="1"/>
-    <col min="16" max="16" width="11.625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="11" customWidth="1"/>
+    <col min="13" max="13" width="13.875" style="11" customWidth="1"/>
+    <col min="14" max="15" width="4.375" style="11" customWidth="1"/>
+    <col min="16" max="16" width="11.625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
     </row>
     <row r="3" spans="1:19" ht="6.75" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="30"/>
+      <c r="G4" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="30"/>
+      <c r="G5" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="2" t="s">
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="26" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="24" t="s">
+    <row r="8" spans="1:19" s="22" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="18">
+      <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="18" t="str">
+      <c r="B9" s="14" t="str">
         <f>RawData!B6</f>
         <v>강남대로</v>
       </c>
-      <c r="C9" s="18" t="str">
+      <c r="C9" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A6</f>
         <v>25-서초구-1</v>
       </c>
-      <c r="D9" s="18" t="str">
+      <c r="D9" s="14" t="str">
         <f>RawData!D6</f>
         <v>양호</v>
       </c>
-      <c r="E9" s="18" t="str">
+      <c r="E9" s="14" t="str">
         <f>RawData!E6</f>
         <v>-</v>
       </c>
-      <c r="F9" s="18" t="str">
+      <c r="F9" s="14" t="str">
         <f>RawData!F6</f>
         <v>양호</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="14">
         <f>RawData!G6</f>
         <v>2</v>
       </c>
-      <c r="H9" s="18" t="str">
+      <c r="H9" s="14" t="str">
         <f>RawData!H6</f>
         <v>-</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="14">
         <f t="shared" ref="I9:I48" si="0">IF(D9="양호",0,IF(D9&gt;=100,9,IF(D9&gt;=50,3,IF(D9&lt;50,0))))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="14">
         <f t="shared" ref="J9:J48" si="1">IF(E9="거북등",3,IF(RIGHT(E9,2)="균열",1,IF(E9="-",0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="14">
         <f t="shared" ref="K9:K48" si="2">IF(F9="유출",9,IF(F9="습윤",1,IF(F9="양호",0,IF(F9="건조",0))))</f>
         <v>0</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="14">
         <f t="shared" ref="L9:L48" si="3">IF(G9&lt;10,0,IF(G9&lt;30,1,IF(G9&gt;=30,2)))</f>
         <v>0</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="14">
         <f t="shared" ref="M9:M48" si="4">IF(H9="-",0,1)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="14">
         <f t="shared" ref="N9:N48" si="5">SUM(I9:M9)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="18" t="str">
+      <c r="O9" s="14" t="str">
         <f t="shared" ref="O9:O48" si="6">IF(N9&lt;6,"일반",IF(N9&lt;9,"우선",IF(N9&gt;=9,"긴급")))</f>
         <v>일반</v>
       </c>
-      <c r="P9" s="18" t="str">
+      <c r="P9" s="14" t="str">
         <f>RawData!P6</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="18">
+      <c r="A10" s="14">
         <v>2</v>
       </c>
-      <c r="B10" s="18" t="str">
+      <c r="B10" s="14" t="str">
         <f>RawData!B7</f>
         <v>강남대로</v>
       </c>
-      <c r="C10" s="18" t="str">
+      <c r="C10" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A7</f>
         <v>25-서초구-2</v>
       </c>
-      <c r="D10" s="18" t="str">
+      <c r="D10" s="14" t="str">
         <f>RawData!D7</f>
         <v>양호</v>
       </c>
-      <c r="E10" s="18" t="str">
+      <c r="E10" s="14" t="str">
         <f>RawData!E7</f>
         <v>거북등</v>
       </c>
-      <c r="F10" s="18" t="str">
+      <c r="F10" s="14" t="str">
         <f>RawData!F7</f>
         <v>양호</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="14">
         <f>RawData!G7</f>
         <v>2</v>
       </c>
-      <c r="H10" s="18" t="str">
+      <c r="H10" s="14" t="str">
         <f>RawData!H7</f>
         <v>-</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M10" s="18">
+      <c r="M10" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O10" s="18" t="str">
+      <c r="O10" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P10" s="18">
+      <c r="P10" s="14">
         <f>RawData!P7</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="18">
+      <c r="A11" s="14">
         <v>3</v>
       </c>
-      <c r="B11" s="18" t="str">
+      <c r="B11" s="14" t="str">
         <f>RawData!B8</f>
         <v>강남대로</v>
       </c>
-      <c r="C11" s="18" t="str">
+      <c r="C11" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A8</f>
         <v>25-서초구-3</v>
       </c>
-      <c r="D11" s="18" t="str">
+      <c r="D11" s="14" t="str">
         <f>RawData!D8</f>
         <v>양호</v>
       </c>
-      <c r="E11" s="18" t="str">
+      <c r="E11" s="14" t="str">
         <f>RawData!E8</f>
         <v>횡균열</v>
       </c>
-      <c r="F11" s="18" t="str">
+      <c r="F11" s="14" t="str">
         <f>RawData!F8</f>
         <v>양호</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="14">
         <f>RawData!G8</f>
         <v>2</v>
       </c>
-      <c r="H11" s="18" t="str">
+      <c r="H11" s="14" t="str">
         <f>RawData!H8</f>
         <v>-</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="14">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O11" s="18" t="str">
+      <c r="O11" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P11" s="18">
+      <c r="P11" s="14">
         <f>RawData!P8</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="18">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="str">
+      <c r="B12" s="14" t="str">
         <f>RawData!B9</f>
         <v>강남대로</v>
       </c>
-      <c r="C12" s="18" t="str">
+      <c r="C12" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A9</f>
         <v>25-서초구-4</v>
       </c>
-      <c r="D12" s="18" t="str">
+      <c r="D12" s="14" t="str">
         <f>RawData!D9</f>
         <v>양호</v>
       </c>
-      <c r="E12" s="18" t="str">
+      <c r="E12" s="14" t="str">
         <f>RawData!E9</f>
         <v>거북등</v>
       </c>
-      <c r="F12" s="18" t="str">
+      <c r="F12" s="14" t="str">
         <f>RawData!F9</f>
         <v>양호</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="14">
         <f>RawData!G9</f>
         <v>2</v>
       </c>
-      <c r="H12" s="18" t="str">
+      <c r="H12" s="14" t="str">
         <f>RawData!H9</f>
         <v>-</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O12" s="18" t="str">
+      <c r="O12" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P12" s="18" t="str">
+      <c r="P12" s="14" t="str">
         <f>RawData!P9</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="18">
+      <c r="A13" s="14">
         <v>5</v>
       </c>
-      <c r="B13" s="18" t="str">
+      <c r="B13" s="14" t="str">
         <f>RawData!B10</f>
         <v>강남대로</v>
       </c>
-      <c r="C13" s="18" t="str">
+      <c r="C13" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A10</f>
         <v>25-서초구-5</v>
       </c>
-      <c r="D13" s="18" t="str">
+      <c r="D13" s="14" t="str">
         <f>RawData!D10</f>
         <v>양호</v>
       </c>
-      <c r="E13" s="18" t="str">
+      <c r="E13" s="14" t="str">
         <f>RawData!E10</f>
         <v>-</v>
       </c>
-      <c r="F13" s="18" t="str">
+      <c r="F13" s="14" t="str">
         <f>RawData!F10</f>
         <v>양호</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="14">
         <f>RawData!G10</f>
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="str">
+      <c r="H13" s="14" t="str">
         <f>RawData!H10</f>
         <v>-</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O13" s="18" t="str">
+      <c r="O13" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P13" s="18" t="str">
+      <c r="P13" s="14" t="str">
         <f>RawData!P10</f>
         <v>보도침하</v>
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="18">
+      <c r="A14" s="14">
         <v>6</v>
       </c>
-      <c r="B14" s="18" t="str">
+      <c r="B14" s="14" t="str">
         <f>RawData!B11</f>
         <v>강남대로</v>
       </c>
-      <c r="C14" s="18" t="str">
+      <c r="C14" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A11</f>
         <v>25-서초구-6</v>
       </c>
-      <c r="D14" s="18" t="str">
+      <c r="D14" s="14" t="str">
         <f>RawData!D11</f>
         <v>양호</v>
       </c>
-      <c r="E14" s="18" t="str">
+      <c r="E14" s="14" t="str">
         <f>RawData!E11</f>
         <v>거북등</v>
       </c>
-      <c r="F14" s="18" t="str">
+      <c r="F14" s="14" t="str">
         <f>RawData!F11</f>
         <v>양호</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="14">
         <f>RawData!G11</f>
         <v>2</v>
       </c>
-      <c r="H14" s="18" t="str">
+      <c r="H14" s="14" t="str">
         <f>RawData!H11</f>
         <v>-</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M14" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O14" s="18" t="str">
+      <c r="O14" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P14" s="18" t="str">
+      <c r="P14" s="14" t="str">
         <f>RawData!P11</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="18">
+      <c r="A15" s="14">
         <v>7</v>
       </c>
-      <c r="B15" s="18" t="str">
+      <c r="B15" s="14" t="str">
         <f>RawData!B12</f>
         <v>강남대로</v>
       </c>
-      <c r="C15" s="18" t="str">
+      <c r="C15" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A12</f>
         <v>25-서초구-7</v>
       </c>
-      <c r="D15" s="18" t="str">
+      <c r="D15" s="14" t="str">
         <f>RawData!D12</f>
         <v>양호</v>
       </c>
-      <c r="E15" s="18" t="str">
+      <c r="E15" s="14" t="str">
         <f>RawData!E12</f>
         <v>거북등</v>
       </c>
-      <c r="F15" s="18" t="str">
+      <c r="F15" s="14" t="str">
         <f>RawData!F12</f>
         <v>양호</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="14">
         <f>RawData!G12</f>
         <v>2</v>
       </c>
-      <c r="H15" s="18" t="str">
+      <c r="H15" s="14" t="str">
         <f>RawData!H12</f>
         <v>-</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O15" s="18" t="str">
+      <c r="O15" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P15" s="18" t="str">
+      <c r="P15" s="14" t="str">
         <f>RawData!P12</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="18">
+      <c r="A16" s="14">
         <v>8</v>
       </c>
-      <c r="B16" s="18" t="str">
+      <c r="B16" s="14" t="str">
         <f>RawData!B13</f>
         <v>강남대로</v>
       </c>
-      <c r="C16" s="18" t="str">
+      <c r="C16" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A13</f>
         <v>25-서초구-8</v>
       </c>
-      <c r="D16" s="18" t="str">
+      <c r="D16" s="14" t="str">
         <f>RawData!D13</f>
         <v>양호</v>
       </c>
-      <c r="E16" s="18" t="str">
+      <c r="E16" s="14" t="str">
         <f>RawData!E13</f>
         <v>거북등</v>
       </c>
-      <c r="F16" s="18" t="str">
+      <c r="F16" s="14" t="str">
         <f>RawData!F13</f>
         <v>양호</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="14">
         <f>RawData!G13</f>
         <v>2</v>
       </c>
-      <c r="H16" s="18" t="str">
+      <c r="H16" s="14" t="str">
         <f>RawData!H13</f>
         <v>-</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O16" s="18" t="str">
+      <c r="O16" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P16" s="18" t="str">
+      <c r="P16" s="14" t="str">
         <f>RawData!P13</f>
         <v>버스차선 확인불가</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="18">
+      <c r="A17" s="14">
         <v>9</v>
       </c>
-      <c r="B17" s="18" t="str">
+      <c r="B17" s="14" t="str">
         <f>RawData!B14</f>
         <v>강남대로</v>
       </c>
-      <c r="C17" s="18" t="str">
+      <c r="C17" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A14</f>
         <v>25-서초구-9</v>
       </c>
-      <c r="D17" s="18" t="str">
+      <c r="D17" s="14" t="str">
         <f>RawData!D14</f>
         <v>양호</v>
       </c>
-      <c r="E17" s="18" t="str">
+      <c r="E17" s="14" t="str">
         <f>RawData!E14</f>
         <v>거북등</v>
       </c>
-      <c r="F17" s="18" t="str">
+      <c r="F17" s="14" t="str">
         <f>RawData!F14</f>
         <v>양호</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="14">
         <f>RawData!G14</f>
         <v>2</v>
       </c>
-      <c r="H17" s="18" t="str">
+      <c r="H17" s="14" t="str">
         <f>RawData!H14</f>
         <v>-</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K17" s="18">
+      <c r="K17" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N17" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O17" s="18" t="str">
+      <c r="O17" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P17" s="18" t="str">
+      <c r="P17" s="14" t="str">
         <f>RawData!P14</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="18">
+      <c r="A18" s="14">
         <v>10</v>
       </c>
-      <c r="B18" s="18" t="str">
+      <c r="B18" s="14" t="str">
         <f>RawData!B15</f>
         <v>강남대로</v>
       </c>
-      <c r="C18" s="18" t="str">
+      <c r="C18" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A15</f>
         <v>25-서초구-10</v>
       </c>
-      <c r="D18" s="18" t="str">
+      <c r="D18" s="14" t="str">
         <f>RawData!D15</f>
         <v>양호</v>
       </c>
-      <c r="E18" s="18" t="str">
+      <c r="E18" s="14" t="str">
         <f>RawData!E15</f>
         <v>거북등</v>
       </c>
-      <c r="F18" s="18" t="str">
+      <c r="F18" s="14" t="str">
         <f>RawData!F15</f>
         <v>양호</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="14">
         <f>RawData!G15</f>
         <v>2</v>
       </c>
-      <c r="H18" s="18" t="str">
+      <c r="H18" s="14" t="str">
         <f>RawData!H15</f>
         <v>-</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O18" s="18" t="str">
+      <c r="O18" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P18" s="18">
+      <c r="P18" s="14">
         <f>RawData!P15</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="18">
+      <c r="A19" s="14">
         <v>11</v>
       </c>
-      <c r="B19" s="18" t="str">
+      <c r="B19" s="14" t="str">
         <f>RawData!B16</f>
         <v>강남대로</v>
       </c>
-      <c r="C19" s="18" t="str">
+      <c r="C19" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A16</f>
         <v>25-서초구-11</v>
       </c>
-      <c r="D19" s="18" t="str">
+      <c r="D19" s="14" t="str">
         <f>RawData!D16</f>
         <v>양호</v>
       </c>
-      <c r="E19" s="18" t="str">
+      <c r="E19" s="14" t="str">
         <f>RawData!E16</f>
         <v>거북등</v>
       </c>
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="14" t="str">
         <f>RawData!F16</f>
         <v>양호</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="14">
         <f>RawData!G16</f>
         <v>2</v>
       </c>
-      <c r="H19" s="18" t="str">
+      <c r="H19" s="14" t="str">
         <f>RawData!H16</f>
         <v>-</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K19" s="18">
+      <c r="K19" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="18">
+      <c r="L19" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N19" s="18">
+      <c r="N19" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O19" s="18" t="str">
+      <c r="O19" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P19" s="18" t="str">
+      <c r="P19" s="14" t="str">
         <f>RawData!P16</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="18">
+      <c r="A20" s="14">
         <v>12</v>
       </c>
-      <c r="B20" s="18" t="str">
+      <c r="B20" s="14" t="str">
         <f>RawData!B17</f>
         <v>강남대로</v>
       </c>
-      <c r="C20" s="18" t="str">
+      <c r="C20" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A17</f>
         <v>25-서초구-12</v>
       </c>
-      <c r="D20" s="18" t="str">
+      <c r="D20" s="14" t="str">
         <f>RawData!D17</f>
         <v>양호</v>
       </c>
-      <c r="E20" s="18" t="str">
+      <c r="E20" s="14" t="str">
         <f>RawData!E17</f>
         <v>거북등</v>
       </c>
-      <c r="F20" s="18" t="str">
+      <c r="F20" s="14" t="str">
         <f>RawData!F17</f>
         <v>양호</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="14">
         <f>RawData!G17</f>
         <v>2</v>
       </c>
-      <c r="H20" s="18" t="str">
+      <c r="H20" s="14" t="str">
         <f>RawData!H17</f>
         <v>-</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K20" s="18">
+      <c r="K20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="18">
+      <c r="L20" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O20" s="18" t="str">
+      <c r="O20" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P20" s="18" t="str">
+      <c r="P20" s="14" t="str">
         <f>RawData!P17</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="18">
+      <c r="A21" s="14">
         <v>13</v>
       </c>
-      <c r="B21" s="18" t="str">
+      <c r="B21" s="14" t="str">
         <f>RawData!B18</f>
         <v>강남대로</v>
       </c>
-      <c r="C21" s="18" t="str">
+      <c r="C21" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A18</f>
         <v>25-서초구-13</v>
       </c>
-      <c r="D21" s="18" t="str">
+      <c r="D21" s="14" t="str">
         <f>RawData!D18</f>
         <v>양호</v>
       </c>
-      <c r="E21" s="18" t="str">
+      <c r="E21" s="14" t="str">
         <f>RawData!E18</f>
         <v>거북등</v>
       </c>
-      <c r="F21" s="18" t="str">
+      <c r="F21" s="14" t="str">
         <f>RawData!F18</f>
         <v>양호</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="14">
         <f>RawData!G18</f>
         <v>2</v>
       </c>
-      <c r="H21" s="18" t="str">
+      <c r="H21" s="14" t="str">
         <f>RawData!H18</f>
         <v>-</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O21" s="18" t="str">
+      <c r="O21" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P21" s="18" t="str">
+      <c r="P21" s="14" t="str">
         <f>RawData!P18</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="18">
+      <c r="A22" s="14">
         <v>14</v>
       </c>
-      <c r="B22" s="18" t="str">
+      <c r="B22" s="14" t="str">
         <f>RawData!B19</f>
         <v>강남대로</v>
       </c>
-      <c r="C22" s="18" t="str">
+      <c r="C22" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A19</f>
         <v>25-서초구-14</v>
       </c>
-      <c r="D22" s="18" t="str">
+      <c r="D22" s="14" t="str">
         <f>RawData!D19</f>
         <v>양호</v>
       </c>
-      <c r="E22" s="18" t="str">
+      <c r="E22" s="14" t="str">
         <f>RawData!E19</f>
         <v>-</v>
       </c>
-      <c r="F22" s="18" t="str">
+      <c r="F22" s="14" t="str">
         <f>RawData!F19</f>
         <v>양호</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="14">
         <f>RawData!G19</f>
         <v>2</v>
       </c>
-      <c r="H22" s="18" t="str">
+      <c r="H22" s="14" t="str">
         <f>RawData!H19</f>
         <v>-</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="18">
+      <c r="K22" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="18">
+      <c r="L22" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="18">
+      <c r="M22" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N22" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="18" t="str">
+      <c r="O22" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P22" s="18" t="str">
+      <c r="P22" s="14" t="str">
         <f>RawData!P19</f>
         <v>보도침하(5cm)</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="18">
+      <c r="A23" s="14">
         <v>15</v>
       </c>
-      <c r="B23" s="18" t="str">
+      <c r="B23" s="14" t="str">
         <f>RawData!B20</f>
         <v>강남대로</v>
       </c>
-      <c r="C23" s="18" t="str">
+      <c r="C23" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A20</f>
         <v>25-서초구-15</v>
       </c>
-      <c r="D23" s="18" t="str">
+      <c r="D23" s="14" t="str">
         <f>RawData!D20</f>
         <v>양호</v>
       </c>
-      <c r="E23" s="18" t="str">
+      <c r="E23" s="14" t="str">
         <f>RawData!E20</f>
         <v>거북등</v>
       </c>
-      <c r="F23" s="18" t="str">
+      <c r="F23" s="14" t="str">
         <f>RawData!F20</f>
         <v>양호</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="14">
         <f>RawData!G20</f>
         <v>2</v>
       </c>
-      <c r="H23" s="18" t="str">
+      <c r="H23" s="14" t="str">
         <f>RawData!H20</f>
         <v>-</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O23" s="18" t="str">
+      <c r="O23" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P23" s="18">
+      <c r="P23" s="14">
         <f>RawData!P20</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="18">
+      <c r="A24" s="14">
         <v>16</v>
       </c>
-      <c r="B24" s="18" t="str">
+      <c r="B24" s="14" t="str">
         <f>RawData!B21</f>
         <v>강남대로</v>
       </c>
-      <c r="C24" s="18" t="str">
+      <c r="C24" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A21</f>
         <v>25-서초구-16</v>
       </c>
-      <c r="D24" s="18" t="str">
+      <c r="D24" s="14" t="str">
         <f>RawData!D21</f>
         <v>양호</v>
       </c>
-      <c r="E24" s="18" t="str">
+      <c r="E24" s="14" t="str">
         <f>RawData!E21</f>
         <v>거북등</v>
       </c>
-      <c r="F24" s="18" t="str">
+      <c r="F24" s="14" t="str">
         <f>RawData!F21</f>
         <v>양호</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="14">
         <f>RawData!G21</f>
         <v>2</v>
       </c>
-      <c r="H24" s="18" t="str">
+      <c r="H24" s="14" t="str">
         <f>RawData!H21</f>
         <v>-</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O24" s="18" t="str">
+      <c r="O24" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="14">
         <f>RawData!P21</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="18">
+      <c r="A25" s="14">
         <v>17</v>
       </c>
-      <c r="B25" s="18" t="str">
+      <c r="B25" s="14" t="str">
         <f>RawData!B22</f>
         <v>강남대로</v>
       </c>
-      <c r="C25" s="18" t="str">
+      <c r="C25" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A22</f>
         <v>25-서초구-17</v>
       </c>
-      <c r="D25" s="18" t="str">
+      <c r="D25" s="14" t="str">
         <f>RawData!D22</f>
         <v>양호</v>
       </c>
-      <c r="E25" s="18" t="str">
+      <c r="E25" s="14" t="str">
         <f>RawData!E22</f>
         <v>거북등</v>
       </c>
-      <c r="F25" s="18" t="str">
+      <c r="F25" s="14" t="str">
         <f>RawData!F22</f>
         <v>양호</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="14">
         <f>RawData!G22</f>
         <v>2</v>
       </c>
-      <c r="H25" s="18" t="str">
+      <c r="H25" s="14" t="str">
         <f>RawData!H22</f>
         <v>-</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="18">
+      <c r="L25" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25" s="18">
+      <c r="M25" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O25" s="18" t="str">
+      <c r="O25" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P25" s="18" t="str">
+      <c r="P25" s="14" t="str">
         <f>RawData!P22</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="18">
+      <c r="A26" s="14">
         <v>18</v>
       </c>
-      <c r="B26" s="18" t="str">
+      <c r="B26" s="14" t="str">
         <f>RawData!B23</f>
         <v>강남대로</v>
       </c>
-      <c r="C26" s="18" t="str">
+      <c r="C26" s="14" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A23</f>
         <v>25-서초구-18</v>
       </c>
-      <c r="D26" s="18" t="str">
+      <c r="D26" s="14" t="str">
         <f>RawData!D23</f>
         <v>양호</v>
       </c>
-      <c r="E26" s="18" t="str">
+      <c r="E26" s="14" t="str">
         <f>RawData!E23</f>
         <v>거북등</v>
       </c>
-      <c r="F26" s="18" t="str">
+      <c r="F26" s="14" t="str">
         <f>RawData!F23</f>
         <v>양호</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="14">
         <f>RawData!G23</f>
         <v>2</v>
       </c>
-      <c r="H26" s="18" t="str">
+      <c r="H26" s="14" t="str">
         <f>RawData!H23</f>
         <v>-</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K26" s="18">
+      <c r="K26" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="18">
+      <c r="M26" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="14">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O26" s="18" t="str">
+      <c r="O26" s="14" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P26" s="18">
+      <c r="P26" s="14">
         <f>RawData!P23</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="6.75" customHeight="1">
-      <c r="A27" s="23">
+      <c r="A27" s="19">
         <v>19</v>
       </c>
-      <c r="B27" s="23" t="str">
+      <c r="B27" s="19" t="str">
         <f>RawData!B24</f>
         <v>강남대로</v>
       </c>
-      <c r="C27" s="23" t="str">
+      <c r="C27" s="19" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A24</f>
         <v>25-서초구-19</v>
       </c>
-      <c r="D27" s="23" t="str">
+      <c r="D27" s="19" t="str">
         <f>RawData!D24</f>
         <v>양호</v>
       </c>
-      <c r="E27" s="23" t="str">
+      <c r="E27" s="19" t="str">
         <f>RawData!E24</f>
         <v>거북등</v>
       </c>
-      <c r="F27" s="23" t="str">
+      <c r="F27" s="19" t="str">
         <f>RawData!F24</f>
         <v>양호</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="19">
         <f>RawData!G24</f>
         <v>2</v>
       </c>
-      <c r="H27" s="23" t="str">
+      <c r="H27" s="19" t="str">
         <f>RawData!H24</f>
         <v>-</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="19">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="23">
+      <c r="L27" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N27" s="23">
+      <c r="N27" s="19">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O27" s="23" t="str">
+      <c r="O27" s="19" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P27" s="23">
+      <c r="P27" s="19">
         <f>RawData!P24</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="27">
+      <c r="A28" s="23">
         <v>20</v>
       </c>
-      <c r="B28" s="17" t="str">
+      <c r="B28" s="13" t="str">
         <f>RawData!B25</f>
         <v>강남대로</v>
       </c>
-      <c r="C28" s="25" t="str">
+      <c r="C28" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A25</f>
         <v>25-서초구-20</v>
       </c>
-      <c r="D28" s="25" t="str">
+      <c r="D28" s="21" t="str">
         <f>RawData!D25</f>
         <v>양호</v>
       </c>
-      <c r="E28" s="25" t="str">
+      <c r="E28" s="21" t="str">
         <f>RawData!E25</f>
         <v>종균열</v>
       </c>
-      <c r="F28" s="25" t="str">
+      <c r="F28" s="21" t="str">
         <f>RawData!F25</f>
         <v>양호</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="21">
         <f>RawData!G25</f>
         <v>2</v>
       </c>
-      <c r="H28" s="25" t="str">
+      <c r="H28" s="21" t="str">
         <f>RawData!H25</f>
         <v>-</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="21">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="25">
+      <c r="L28" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="21">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O28" s="25" t="str">
+      <c r="O28" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P28" s="25">
+      <c r="P28" s="21">
         <f>RawData!P25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="25">
+      <c r="A29" s="21">
         <v>21</v>
       </c>
-      <c r="B29" s="25" t="str">
+      <c r="B29" s="21" t="str">
         <f>RawData!B26</f>
         <v>강남대로</v>
       </c>
-      <c r="C29" s="25" t="str">
+      <c r="C29" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A26</f>
         <v>25-서초구-21</v>
       </c>
-      <c r="D29" s="25" t="str">
+      <c r="D29" s="21" t="str">
         <f>RawData!D26</f>
         <v>양호</v>
       </c>
-      <c r="E29" s="25" t="str">
+      <c r="E29" s="21" t="str">
         <f>RawData!E26</f>
         <v>거북등</v>
       </c>
-      <c r="F29" s="25" t="str">
+      <c r="F29" s="21" t="str">
         <f>RawData!F26</f>
         <v>양호</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="21">
         <f>RawData!G26</f>
         <v>2</v>
       </c>
-      <c r="H29" s="25" t="str">
+      <c r="H29" s="21" t="str">
         <f>RawData!H26</f>
         <v>-</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="25">
+      <c r="L29" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O29" s="25" t="str">
+      <c r="O29" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P29" s="25">
+      <c r="P29" s="21">
         <f>RawData!P26</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="25">
+      <c r="A30" s="21">
         <v>22</v>
       </c>
-      <c r="B30" s="25" t="str">
+      <c r="B30" s="21" t="str">
         <f>RawData!B27</f>
         <v>강남대로</v>
       </c>
-      <c r="C30" s="25" t="str">
+      <c r="C30" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A27</f>
         <v>25-서초구-22</v>
       </c>
-      <c r="D30" s="25" t="str">
+      <c r="D30" s="21" t="str">
         <f>RawData!D27</f>
         <v>양호</v>
       </c>
-      <c r="E30" s="25" t="str">
+      <c r="E30" s="21" t="str">
         <f>RawData!E27</f>
         <v>거북등</v>
       </c>
-      <c r="F30" s="25" t="str">
+      <c r="F30" s="21" t="str">
         <f>RawData!F27</f>
         <v>양호</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="21">
         <f>RawData!G27</f>
         <v>2</v>
       </c>
-      <c r="H30" s="25" t="str">
+      <c r="H30" s="21" t="str">
         <f>RawData!H27</f>
         <v>-</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="25">
+      <c r="L30" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O30" s="25" t="str">
+      <c r="O30" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P30" s="25">
+      <c r="P30" s="21">
         <f>RawData!P27</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="25">
+      <c r="A31" s="21">
         <v>23</v>
       </c>
-      <c r="B31" s="25" t="str">
+      <c r="B31" s="21" t="str">
         <f>RawData!B28</f>
         <v>강남대로</v>
       </c>
-      <c r="C31" s="25" t="str">
+      <c r="C31" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A28</f>
         <v>25-서초구-23</v>
       </c>
-      <c r="D31" s="25" t="str">
+      <c r="D31" s="21" t="str">
         <f>RawData!D28</f>
         <v>양호</v>
       </c>
-      <c r="E31" s="25" t="str">
+      <c r="E31" s="21" t="str">
         <f>RawData!E28</f>
         <v>-</v>
       </c>
-      <c r="F31" s="25" t="str">
+      <c r="F31" s="21" t="str">
         <f>RawData!F28</f>
         <v>양호</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="21">
         <f>RawData!G28</f>
         <v>2</v>
       </c>
-      <c r="H31" s="25" t="str">
+      <c r="H31" s="21" t="str">
         <f>RawData!H28</f>
         <v>-</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K31" s="25">
+      <c r="K31" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="25">
+      <c r="L31" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="25">
+      <c r="M31" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O31" s="25" t="str">
+      <c r="O31" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P31" s="25" t="str">
+      <c r="P31" s="21" t="str">
         <f>RawData!P28</f>
         <v>보도침하</v>
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="25">
+      <c r="A32" s="21">
         <v>24</v>
       </c>
-      <c r="B32" s="25" t="str">
+      <c r="B32" s="21" t="str">
         <f>RawData!B29</f>
         <v>강남대로</v>
       </c>
-      <c r="C32" s="25" t="str">
+      <c r="C32" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A29</f>
         <v>25-서초구-24</v>
       </c>
-      <c r="D32" s="25" t="str">
+      <c r="D32" s="21" t="str">
         <f>RawData!D29</f>
         <v>양호</v>
       </c>
-      <c r="E32" s="25" t="str">
+      <c r="E32" s="21" t="str">
         <f>RawData!E29</f>
         <v>거북등</v>
       </c>
-      <c r="F32" s="25" t="str">
+      <c r="F32" s="21" t="str">
         <f>RawData!F29</f>
         <v>양호</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="21">
         <f>RawData!G29</f>
         <v>2</v>
       </c>
-      <c r="H32" s="25" t="str">
+      <c r="H32" s="21" t="str">
         <f>RawData!H29</f>
         <v>-</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O32" s="25" t="str">
+      <c r="O32" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P32" s="25">
+      <c r="P32" s="21">
         <f>RawData!P29</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="25">
+      <c r="A33" s="21">
         <v>25</v>
       </c>
-      <c r="B33" s="25" t="str">
+      <c r="B33" s="21" t="str">
         <f>RawData!B30</f>
         <v>강남대로</v>
       </c>
-      <c r="C33" s="25" t="str">
+      <c r="C33" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A30</f>
         <v>25-서초구-25</v>
       </c>
-      <c r="D33" s="25" t="str">
+      <c r="D33" s="21" t="str">
         <f>RawData!D30</f>
         <v>양호</v>
       </c>
-      <c r="E33" s="25" t="str">
+      <c r="E33" s="21" t="str">
         <f>RawData!E30</f>
         <v>거북등</v>
       </c>
-      <c r="F33" s="25" t="str">
+      <c r="F33" s="21" t="str">
         <f>RawData!F30</f>
         <v>양호</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="21">
         <f>RawData!G30</f>
         <v>2</v>
       </c>
-      <c r="H33" s="25" t="str">
+      <c r="H33" s="21" t="str">
         <f>RawData!H30</f>
         <v>-</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="25">
+      <c r="L33" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N33" s="25">
+      <c r="N33" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O33" s="25" t="str">
+      <c r="O33" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P33" s="25">
+      <c r="P33" s="21">
         <f>RawData!P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="25">
+      <c r="A34" s="21">
         <v>26</v>
       </c>
-      <c r="B34" s="25" t="str">
+      <c r="B34" s="21" t="str">
         <f>RawData!B31</f>
         <v>강남대로</v>
       </c>
-      <c r="C34" s="25" t="str">
+      <c r="C34" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A31</f>
         <v>25-서초구-26</v>
       </c>
-      <c r="D34" s="25" t="str">
+      <c r="D34" s="21" t="str">
         <f>RawData!D31</f>
         <v>양호</v>
       </c>
-      <c r="E34" s="25" t="str">
+      <c r="E34" s="21" t="str">
         <f>RawData!E31</f>
         <v>거북등</v>
       </c>
-      <c r="F34" s="25" t="str">
+      <c r="F34" s="21" t="str">
         <f>RawData!F31</f>
         <v>양호</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="21">
         <f>RawData!G31</f>
         <v>2</v>
       </c>
-      <c r="H34" s="25" t="str">
+      <c r="H34" s="21" t="str">
         <f>RawData!H31</f>
         <v>-</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="25">
+      <c r="L34" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N34" s="25">
+      <c r="N34" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O34" s="25" t="str">
+      <c r="O34" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P34" s="25">
+      <c r="P34" s="21">
         <f>RawData!P31</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="25">
+      <c r="A35" s="21">
         <v>27</v>
       </c>
-      <c r="B35" s="25" t="str">
+      <c r="B35" s="21" t="str">
         <f>RawData!B32</f>
         <v>강남대로</v>
       </c>
-      <c r="C35" s="25" t="str">
+      <c r="C35" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A32</f>
         <v>25-서초구-27</v>
       </c>
-      <c r="D35" s="25" t="str">
+      <c r="D35" s="21" t="str">
         <f>RawData!D32</f>
         <v>양호</v>
       </c>
-      <c r="E35" s="25" t="str">
+      <c r="E35" s="21" t="str">
         <f>RawData!E32</f>
         <v>종균열</v>
       </c>
-      <c r="F35" s="25" t="str">
+      <c r="F35" s="21" t="str">
         <f>RawData!F32</f>
         <v>양호</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="21">
         <f>RawData!G32</f>
         <v>2</v>
       </c>
-      <c r="H35" s="25" t="str">
+      <c r="H35" s="21" t="str">
         <f>RawData!H32</f>
         <v>-</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="21">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N35" s="25">
+      <c r="N35" s="21">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O35" s="25" t="str">
+      <c r="O35" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P35" s="25">
+      <c r="P35" s="21">
         <f>RawData!P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="25">
+      <c r="A36" s="21">
         <v>28</v>
       </c>
-      <c r="B36" s="25" t="str">
+      <c r="B36" s="21" t="str">
         <f>RawData!B33</f>
         <v>강남대로</v>
       </c>
-      <c r="C36" s="25" t="str">
+      <c r="C36" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A33</f>
         <v>25-서초구-28</v>
       </c>
-      <c r="D36" s="25" t="str">
+      <c r="D36" s="21" t="str">
         <f>RawData!D33</f>
         <v>양호</v>
       </c>
-      <c r="E36" s="25" t="str">
+      <c r="E36" s="21" t="str">
         <f>RawData!E33</f>
         <v>거북등</v>
       </c>
-      <c r="F36" s="25" t="str">
+      <c r="F36" s="21" t="str">
         <f>RawData!F33</f>
         <v>양호</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="21">
         <f>RawData!G33</f>
         <v>2</v>
       </c>
-      <c r="H36" s="25" t="str">
+      <c r="H36" s="21" t="str">
         <f>RawData!H33</f>
         <v>-</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="25">
+      <c r="L36" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M36" s="25">
+      <c r="M36" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N36" s="25">
+      <c r="N36" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O36" s="25" t="str">
+      <c r="O36" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P36" s="25">
+      <c r="P36" s="21">
         <f>RawData!P33</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="25">
+      <c r="A37" s="21">
         <v>29</v>
       </c>
-      <c r="B37" s="25" t="str">
+      <c r="B37" s="21" t="str">
         <f>RawData!B34</f>
         <v>강남대로</v>
       </c>
-      <c r="C37" s="25" t="str">
+      <c r="C37" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A34</f>
         <v>25-서초구-29</v>
       </c>
-      <c r="D37" s="25" t="str">
+      <c r="D37" s="21" t="str">
         <f>RawData!D34</f>
         <v>양호</v>
       </c>
-      <c r="E37" s="25" t="str">
+      <c r="E37" s="21" t="str">
         <f>RawData!E34</f>
         <v>거북등</v>
       </c>
-      <c r="F37" s="25" t="str">
+      <c r="F37" s="21" t="str">
         <f>RawData!F34</f>
         <v>양호</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="21">
         <f>RawData!G34</f>
         <v>2</v>
       </c>
-      <c r="H37" s="25" t="str">
+      <c r="H37" s="21" t="str">
         <f>RawData!H34</f>
         <v>-</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L37" s="25">
+      <c r="L37" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N37" s="25">
+      <c r="N37" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O37" s="25" t="str">
+      <c r="O37" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P37" s="25">
+      <c r="P37" s="21">
         <f>RawData!P34</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="25">
+      <c r="A38" s="21">
         <v>30</v>
       </c>
-      <c r="B38" s="25" t="str">
+      <c r="B38" s="21" t="str">
         <f>RawData!B35</f>
         <v>강남대로</v>
       </c>
-      <c r="C38" s="25" t="str">
+      <c r="C38" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A35</f>
         <v>25-서초구-30</v>
       </c>
-      <c r="D38" s="25" t="str">
+      <c r="D38" s="21" t="str">
         <f>RawData!D35</f>
         <v>양호</v>
       </c>
-      <c r="E38" s="25" t="str">
+      <c r="E38" s="21" t="str">
         <f>RawData!E35</f>
         <v>거북등</v>
       </c>
-      <c r="F38" s="25" t="str">
+      <c r="F38" s="21" t="str">
         <f>RawData!F35</f>
         <v>양호</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="21">
         <f>RawData!G35</f>
         <v>2</v>
       </c>
-      <c r="H38" s="25" t="str">
+      <c r="H38" s="21" t="str">
         <f>RawData!H35</f>
         <v>-</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L38" s="25">
+      <c r="L38" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M38" s="25">
+      <c r="M38" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N38" s="25">
+      <c r="N38" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O38" s="25" t="str">
+      <c r="O38" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P38" s="25" t="str">
+      <c r="P38" s="21" t="str">
         <f>RawData!P35</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="25">
+      <c r="A39" s="21">
         <v>31</v>
       </c>
-      <c r="B39" s="25" t="str">
+      <c r="B39" s="21" t="str">
         <f>RawData!B36</f>
         <v>강남대로</v>
       </c>
-      <c r="C39" s="25" t="str">
+      <c r="C39" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A36</f>
         <v>25-서초구-31</v>
       </c>
-      <c r="D39" s="25" t="str">
+      <c r="D39" s="21" t="str">
         <f>RawData!D36</f>
         <v>양호</v>
       </c>
-      <c r="E39" s="25" t="str">
+      <c r="E39" s="21" t="str">
         <f>RawData!E36</f>
         <v>거북등</v>
       </c>
-      <c r="F39" s="25" t="str">
+      <c r="F39" s="21" t="str">
         <f>RawData!F36</f>
         <v>양호</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="21">
         <f>RawData!G36</f>
         <v>2</v>
       </c>
-      <c r="H39" s="25" t="str">
+      <c r="H39" s="21" t="str">
         <f>RawData!H36</f>
         <v>-</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L39" s="25">
+      <c r="L39" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O39" s="25" t="str">
+      <c r="O39" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P39" s="25" t="str">
+      <c r="P39" s="21" t="str">
         <f>RawData!P36</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="25">
+      <c r="A40" s="21">
         <v>32</v>
       </c>
-      <c r="B40" s="25" t="str">
+      <c r="B40" s="21" t="str">
         <f>RawData!B37</f>
         <v>강남대로</v>
       </c>
-      <c r="C40" s="25" t="str">
+      <c r="C40" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A37</f>
         <v>25-서초구-32</v>
       </c>
-      <c r="D40" s="25" t="str">
+      <c r="D40" s="21" t="str">
         <f>RawData!D37</f>
         <v>양호</v>
       </c>
-      <c r="E40" s="25" t="str">
+      <c r="E40" s="21" t="str">
         <f>RawData!E37</f>
         <v>-</v>
       </c>
-      <c r="F40" s="25" t="str">
+      <c r="F40" s="21" t="str">
         <f>RawData!F37</f>
         <v>-</v>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="21">
         <f>RawData!G37</f>
         <v>2</v>
       </c>
-      <c r="H40" s="25" t="str">
+      <c r="H40" s="21" t="str">
         <f>RawData!H37</f>
         <v>-</v>
       </c>
-      <c r="I40" s="25">
+      <c r="I40" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K40" s="28" t="b">
+      <c r="K40" s="24" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L40" s="25">
+      <c r="L40" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M40" s="25">
+      <c r="M40" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N40" s="25">
+      <c r="N40" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O40" s="25" t="str">
+      <c r="O40" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P40" s="25" t="str">
+      <c r="P40" s="21" t="str">
         <f>RawData!P37</f>
         <v>보도침하</v>
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="25">
+      <c r="A41" s="21">
         <v>33</v>
       </c>
-      <c r="B41" s="25" t="str">
+      <c r="B41" s="21" t="str">
         <f>RawData!B38</f>
         <v>강남대로</v>
       </c>
-      <c r="C41" s="25" t="str">
+      <c r="C41" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A38</f>
         <v>25-서초구-33</v>
       </c>
-      <c r="D41" s="25" t="str">
+      <c r="D41" s="21" t="str">
         <f>RawData!D38</f>
         <v>양호</v>
       </c>
-      <c r="E41" s="25" t="str">
+      <c r="E41" s="21" t="str">
         <f>RawData!E38</f>
         <v>거북등</v>
       </c>
-      <c r="F41" s="25" t="str">
+      <c r="F41" s="21" t="str">
         <f>RawData!F38</f>
         <v>양호</v>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="21">
         <f>RawData!G38</f>
         <v>2</v>
       </c>
-      <c r="H41" s="25" t="str">
+      <c r="H41" s="21" t="str">
         <f>RawData!H38</f>
         <v>-</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J41" s="25">
+      <c r="J41" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L41" s="25">
+      <c r="L41" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M41" s="25">
+      <c r="M41" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N41" s="25">
+      <c r="N41" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O41" s="25" t="str">
+      <c r="O41" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P41" s="25">
+      <c r="P41" s="21">
         <f>RawData!P38</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="25">
+      <c r="A42" s="21">
         <v>34</v>
       </c>
-      <c r="B42" s="25" t="str">
+      <c r="B42" s="21" t="str">
         <f>RawData!B39</f>
         <v>강남대로</v>
       </c>
-      <c r="C42" s="25" t="str">
+      <c r="C42" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A39</f>
         <v>25-서초구-34</v>
       </c>
-      <c r="D42" s="25" t="str">
+      <c r="D42" s="21" t="str">
         <f>RawData!D39</f>
         <v>양호</v>
       </c>
-      <c r="E42" s="25" t="str">
+      <c r="E42" s="21" t="str">
         <f>RawData!E39</f>
         <v>거북등</v>
       </c>
-      <c r="F42" s="25" t="str">
+      <c r="F42" s="21" t="str">
         <f>RawData!F39</f>
         <v>양호</v>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="21">
         <f>RawData!G39</f>
         <v>2</v>
       </c>
-      <c r="H42" s="25" t="str">
+      <c r="H42" s="21" t="str">
         <f>RawData!H39</f>
         <v>-</v>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J42" s="25">
+      <c r="J42" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K42" s="25">
+      <c r="K42" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L42" s="25">
+      <c r="L42" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M42" s="25">
+      <c r="M42" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N42" s="25">
+      <c r="N42" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O42" s="25" t="str">
+      <c r="O42" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P42" s="25">
+      <c r="P42" s="21">
         <f>RawData!P39</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="25">
+      <c r="A43" s="21">
         <v>35</v>
       </c>
-      <c r="B43" s="25" t="str">
+      <c r="B43" s="21" t="str">
         <f>RawData!B40</f>
         <v>강남대로</v>
       </c>
-      <c r="C43" s="25" t="str">
+      <c r="C43" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A40</f>
         <v>25-서초구-35</v>
       </c>
-      <c r="D43" s="25" t="str">
+      <c r="D43" s="21" t="str">
         <f>RawData!D40</f>
         <v>양호</v>
       </c>
-      <c r="E43" s="25" t="str">
+      <c r="E43" s="21" t="str">
         <f>RawData!E40</f>
         <v>거북등</v>
       </c>
-      <c r="F43" s="25" t="str">
+      <c r="F43" s="21" t="str">
         <f>RawData!F40</f>
         <v>양호</v>
       </c>
-      <c r="G43" s="25">
+      <c r="G43" s="21">
         <f>RawData!G40</f>
         <v>2</v>
       </c>
-      <c r="H43" s="25" t="str">
+      <c r="H43" s="21" t="str">
         <f>RawData!H40</f>
         <v>-</v>
       </c>
-      <c r="I43" s="25">
+      <c r="I43" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="25">
+      <c r="J43" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K43" s="25">
+      <c r="K43" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L43" s="25">
+      <c r="L43" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M43" s="25">
+      <c r="M43" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O43" s="25" t="str">
+      <c r="O43" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P43" s="25">
+      <c r="P43" s="21">
         <f>RawData!P40</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="25">
+      <c r="A44" s="21">
         <v>36</v>
       </c>
-      <c r="B44" s="25" t="str">
+      <c r="B44" s="21" t="str">
         <f>RawData!B41</f>
         <v>강남대로</v>
       </c>
-      <c r="C44" s="25" t="str">
+      <c r="C44" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A41</f>
         <v>25-서초구-36</v>
       </c>
-      <c r="D44" s="25" t="str">
+      <c r="D44" s="21" t="str">
         <f>RawData!D41</f>
         <v>양호</v>
       </c>
-      <c r="E44" s="25" t="str">
+      <c r="E44" s="21" t="str">
         <f>RawData!E41</f>
         <v>거북등</v>
       </c>
-      <c r="F44" s="25" t="str">
+      <c r="F44" s="21" t="str">
         <f>RawData!F41</f>
         <v>양호</v>
       </c>
-      <c r="G44" s="25">
+      <c r="G44" s="21">
         <f>RawData!G41</f>
         <v>2</v>
       </c>
-      <c r="H44" s="25" t="str">
+      <c r="H44" s="21" t="str">
         <f>RawData!H41</f>
         <v>-</v>
       </c>
-      <c r="I44" s="25">
+      <c r="I44" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J44" s="25">
+      <c r="J44" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K44" s="25">
+      <c r="K44" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L44" s="25">
+      <c r="L44" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M44" s="25">
+      <c r="M44" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N44" s="25">
+      <c r="N44" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O44" s="25" t="str">
+      <c r="O44" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P44" s="25">
+      <c r="P44" s="21">
         <f>RawData!P41</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="25">
+      <c r="A45" s="21">
         <v>37</v>
       </c>
-      <c r="B45" s="25" t="str">
+      <c r="B45" s="21" t="str">
         <f>RawData!B42</f>
         <v>강남대로</v>
       </c>
-      <c r="C45" s="25" t="str">
+      <c r="C45" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A42</f>
         <v>25-서초구-37</v>
       </c>
-      <c r="D45" s="25" t="str">
+      <c r="D45" s="21" t="str">
         <f>RawData!D42</f>
         <v>양호</v>
       </c>
-      <c r="E45" s="25" t="str">
+      <c r="E45" s="21" t="str">
         <f>RawData!E42</f>
         <v>거북등</v>
       </c>
-      <c r="F45" s="25" t="str">
+      <c r="F45" s="21" t="str">
         <f>RawData!F42</f>
         <v>양호</v>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="21">
         <f>RawData!G42</f>
         <v>2</v>
       </c>
-      <c r="H45" s="25" t="str">
+      <c r="H45" s="21" t="str">
         <f>RawData!H42</f>
         <v>-</v>
       </c>
-      <c r="I45" s="25">
+      <c r="I45" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K45" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L45" s="25">
+      <c r="L45" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M45" s="25">
+      <c r="M45" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N45" s="25">
+      <c r="N45" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O45" s="25" t="str">
+      <c r="O45" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P45" s="25">
+      <c r="P45" s="21">
         <f>RawData!P42</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="25">
+      <c r="A46" s="21">
         <v>38</v>
       </c>
-      <c r="B46" s="25" t="str">
+      <c r="B46" s="21" t="str">
         <f>RawData!B43</f>
         <v>강남대로</v>
       </c>
-      <c r="C46" s="25" t="str">
+      <c r="C46" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A43</f>
         <v>25-서초구-38</v>
       </c>
-      <c r="D46" s="25" t="str">
+      <c r="D46" s="21" t="str">
         <f>RawData!D43</f>
         <v>보통</v>
       </c>
-      <c r="E46" s="25" t="str">
+      <c r="E46" s="21" t="str">
         <f>RawData!E43</f>
         <v>-</v>
       </c>
-      <c r="F46" s="25" t="str">
+      <c r="F46" s="21" t="str">
         <f>RawData!F43</f>
         <v>양호</v>
       </c>
-      <c r="G46" s="25">
+      <c r="G46" s="21">
         <f>RawData!G43</f>
         <v>2</v>
       </c>
-      <c r="H46" s="25" t="str">
+      <c r="H46" s="21" t="str">
         <f>RawData!H43</f>
         <v>-</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="21">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J46" s="25">
+      <c r="J46" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="21">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="O46" s="25" t="str">
+      <c r="O46" s="21" t="str">
         <f t="shared" si="6"/>
         <v>긴급</v>
       </c>
-      <c r="P46" s="25" t="str">
+      <c r="P46" s="21" t="str">
         <f>RawData!P43</f>
         <v>5cm이상 침하</v>
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="25">
+      <c r="A47" s="21">
         <v>39</v>
       </c>
-      <c r="B47" s="25" t="str">
+      <c r="B47" s="21" t="str">
         <f>RawData!B44</f>
         <v>강남대로</v>
       </c>
-      <c r="C47" s="25" t="str">
+      <c r="C47" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A44</f>
         <v>25-서초구-39</v>
       </c>
-      <c r="D47" s="25" t="str">
+      <c r="D47" s="21" t="str">
         <f>RawData!D44</f>
         <v>양호</v>
       </c>
-      <c r="E47" s="25" t="str">
+      <c r="E47" s="21" t="str">
         <f>RawData!E44</f>
         <v>거북등</v>
       </c>
-      <c r="F47" s="25" t="str">
+      <c r="F47" s="21" t="str">
         <f>RawData!F44</f>
         <v>양호</v>
       </c>
-      <c r="G47" s="25">
+      <c r="G47" s="21">
         <f>RawData!G44</f>
         <v>2</v>
       </c>
-      <c r="H47" s="25" t="str">
+      <c r="H47" s="21" t="str">
         <f>RawData!H44</f>
         <v>-</v>
       </c>
-      <c r="I47" s="25">
+      <c r="I47" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K47" s="25">
+      <c r="K47" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L47" s="25">
+      <c r="L47" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M47" s="25">
+      <c r="M47" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N47" s="25">
+      <c r="N47" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O47" s="25" t="str">
+      <c r="O47" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P47" s="25">
+      <c r="P47" s="21">
         <f>RawData!P44</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" s="25">
+      <c r="A48" s="21">
         <v>40</v>
       </c>
-      <c r="B48" s="25" t="str">
+      <c r="B48" s="21" t="str">
         <f>RawData!B45</f>
         <v>강남대로</v>
       </c>
-      <c r="C48" s="25" t="str">
+      <c r="C48" s="21" t="str">
         <f>RIGHT(RawData!$A$2,2)&amp;"-"&amp;RawData!$C$2&amp;"-"&amp;RawData!A45</f>
         <v>25-서초구-40</v>
       </c>
-      <c r="D48" s="25" t="str">
+      <c r="D48" s="21" t="str">
         <f>RawData!D45</f>
         <v>양호</v>
       </c>
-      <c r="E48" s="25" t="str">
+      <c r="E48" s="21" t="str">
         <f>RawData!E45</f>
         <v>거북등</v>
       </c>
-      <c r="F48" s="25" t="str">
+      <c r="F48" s="21" t="str">
         <f>RawData!F45</f>
         <v>양호</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G48" s="21">
         <f>RawData!G45</f>
         <v>2</v>
       </c>
-      <c r="H48" s="25" t="str">
+      <c r="H48" s="21" t="str">
         <f>RawData!H45</f>
         <v>-</v>
       </c>
-      <c r="I48" s="25">
+      <c r="I48" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="25">
+      <c r="J48" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K48" s="25">
+      <c r="K48" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L48" s="25">
+      <c r="L48" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M48" s="25">
+      <c r="M48" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N48" s="25">
+      <c r="N48" s="21">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O48" s="25" t="str">
+      <c r="O48" s="21" t="str">
         <f t="shared" si="6"/>
         <v>일반</v>
       </c>
-      <c r="P48" s="25" t="str">
+      <c r="P48" s="21" t="str">
         <f>RawData!P45</f>
         <v>5cm미만 침하</v>
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="25"/>
-      <c r="N49" s="25"/>
-      <c r="O49" s="25"/>
-      <c r="P49" s="25"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+      <c r="P49" s="21"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="25"/>
-      <c r="M50" s="25"/>
-      <c r="N50" s="25"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="25"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -14719,186 +14935,186 @@
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="10.375" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="16384" width="10.375" style="7"/>
+    <col min="1" max="16384" width="10.375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="7">
+      <c r="A2" s="3">
         <v>2018</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
         <v>3</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="3">
         <v>9</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="25" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>2019</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
         <v>1</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="3">
         <v>3</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>2020</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7">
-        <v>0</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="3">
         <v>9</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>2021</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>2022</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>2023</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>2024</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>2025</v>
       </c>
     </row>

--- a/25-새서울철도-서초구-보고서.xlsx
+++ b/25-새서울철도-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3473,9 +3473,381 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>26-10</v>
+      </c>
+      <c r="B52" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C52" t="str">
+        <v>26-서초구-10</v>
+      </c>
+      <c r="D52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E52" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G52" t="str">
+        <v>3</v>
+      </c>
+      <c r="H52" t="str">
+        <v>-</v>
+      </c>
+      <c r="I52" t="str">
+        <v>0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>3</v>
+      </c>
+      <c r="K52" t="str">
+        <v>0</v>
+      </c>
+      <c r="L52" t="str">
+        <v>0</v>
+      </c>
+      <c r="M52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N52" t="str">
+        <v>3</v>
+      </c>
+      <c r="O52" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P52" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>잠원동28-10</v>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v>HY빌딩 앞 도로(강남대로577)</v>
+      </c>
+      <c r="T52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B53" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C53" t="str">
+        <v>26-서초구-11</v>
+      </c>
+      <c r="D53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E53" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G53" t="str">
+        <v>3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>3</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0</v>
+      </c>
+      <c r="L53" t="str">
+        <v>0</v>
+      </c>
+      <c r="M53" t="str">
+        <v>0</v>
+      </c>
+      <c r="N53" t="str">
+        <v>3</v>
+      </c>
+      <c r="O53" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P53" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>잠원동28-6</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v>인접공사현장 앞 도로(강남대로573)</v>
+      </c>
+      <c r="T53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>26-12</v>
+      </c>
+      <c r="B54" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C54" t="str">
+        <v>26-서초구-12</v>
+      </c>
+      <c r="D54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E54" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G54" t="str">
+        <v>3</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>3</v>
+      </c>
+      <c r="K54" t="str">
+        <v>0</v>
+      </c>
+      <c r="L54" t="str">
+        <v>0</v>
+      </c>
+      <c r="M54" t="str">
+        <v>0</v>
+      </c>
+      <c r="N54" t="str">
+        <v>3</v>
+      </c>
+      <c r="O54" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P54" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>잠원동36-13</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v>더뉴치과의원 앞 도로(강남대로567)</v>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C55" t="str">
+        <v>26-서초구-13</v>
+      </c>
+      <c r="D55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G55" t="str">
+        <v>3</v>
+      </c>
+      <c r="H55" t="str">
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>0</v>
+      </c>
+      <c r="K55" t="str">
+        <v>0</v>
+      </c>
+      <c r="L55" t="str">
+        <v>0</v>
+      </c>
+      <c r="M55" t="str">
+        <v>0</v>
+      </c>
+      <c r="N55" t="str">
+        <v>0</v>
+      </c>
+      <c r="O55" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P55" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>잠원동36-13</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v>버스전용차선 (강남대로567)</v>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>26-14</v>
+      </c>
+      <c r="B56" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C56" t="str">
+        <v>26-서초구-14</v>
+      </c>
+      <c r="D56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E56" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G56" t="str">
+        <v>3</v>
+      </c>
+      <c r="H56" t="str">
+        <v>-</v>
+      </c>
+      <c r="I56" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" t="str">
+        <v>3</v>
+      </c>
+      <c r="K56" t="str">
+        <v>0</v>
+      </c>
+      <c r="L56" t="str">
+        <v>0</v>
+      </c>
+      <c r="M56" t="str">
+        <v>0</v>
+      </c>
+      <c r="N56" t="str">
+        <v>3</v>
+      </c>
+      <c r="O56" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P56" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>잠원동37-6</v>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v>정인빌딩 광주은행 앞 도로(강남대로559)</v>
+      </c>
+      <c r="T56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B57" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C57" t="str">
+        <v>26-서초구-15</v>
+      </c>
+      <c r="D57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E57" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G57" t="str">
+        <v>3</v>
+      </c>
+      <c r="H57" t="str">
+        <v>-</v>
+      </c>
+      <c r="I57" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" t="str">
+        <v>3</v>
+      </c>
+      <c r="K57" t="str">
+        <v>0</v>
+      </c>
+      <c r="L57" t="str">
+        <v>0</v>
+      </c>
+      <c r="M57" t="str">
+        <v>0</v>
+      </c>
+      <c r="N57" t="str">
+        <v>3</v>
+      </c>
+      <c r="O57" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P57" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>논현역교차로</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v>논현역 교차로(학동로102)</v>
+      </c>
+      <c r="T57" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T57"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-새서울철도-서초구-보고서.xlsx
+++ b/25-새서울철도-서초구-보고서.xlsx
@@ -485,19 +485,19 @@
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-4</v>
+        <v>25-서초구-5</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
       </c>
       <c r="E5" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F5" t="str">
         <v>양호</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -524,13 +524,13 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="str">
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>5cm미만 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q5" t="str">
         <v>잠원동 21-2</v>
@@ -539,792 +539,791 @@
         <v/>
       </c>
       <c r="S5" t="str" xml:space="preserve">
-        <v xml:space="preserve">CELL TRION 앞_x000d_
-도로_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C6" t="str">
-        <v>25-서초구-5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E6" t="str">
-        <v>-</v>
-      </c>
-      <c r="F6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2</v>
-      </c>
-      <c r="H6" t="str">
-        <v>-</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P6" t="str">
-        <v>보도침하</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>잠원동 21-2</v>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">CELL TRION 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="B6" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C6" t="str">
         <v>25-서초구-6</v>
       </c>
-      <c r="D7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E7" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="D6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E6" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G6" t="str">
         <v>2</v>
       </c>
-      <c r="H7" t="str">
-        <v>-</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
-      <c r="O7" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P7" t="str">
+      <c r="H6" t="str">
+        <v>-</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P6" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="Q6" t="str">
         <v>잠원동 21-3</v>
       </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str" xml:space="preserve">
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">서울미소그린치과 앞_x000d_
 버스정류장_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
+      <c r="T6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="B7" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C7" t="str">
         <v>25-서초구-7</v>
       </c>
-      <c r="D8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E8" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="D7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E7" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G7" t="str">
         <v>2</v>
       </c>
-      <c r="H8" t="str">
-        <v>-</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-      <c r="O8" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P8" t="str">
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P7" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q7" t="str">
         <v>잠원동 21-3</v>
       </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str" xml:space="preserve">
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str" xml:space="preserve">
         <v xml:space="preserve">씨티약국 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B8" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C8" t="str">
         <v>25-서초구-8</v>
       </c>
-      <c r="D9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E9" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="D8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E8" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G8" t="str">
         <v>2</v>
       </c>
-      <c r="H9" t="str">
-        <v>-</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P9" t="str">
+      <c r="H8" t="str">
+        <v>-</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P8" t="str">
         <v>버스차선 확인불가</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="Q8" t="str">
         <v>잠원동 21-7</v>
       </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str" xml:space="preserve">
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str" xml:space="preserve">
         <v xml:space="preserve">스타벅스 앞_x000d_
 버스차선_x000d_
 (강남대로)</v>
       </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
+      <c r="T8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C10" t="str">
+      <c r="B9" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C9" t="str">
         <v>25-서초구-9</v>
       </c>
-      <c r="D10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E10" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="D9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E9" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G9" t="str">
         <v>2</v>
       </c>
-      <c r="H10" t="str">
-        <v>-</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
-      <c r="O10" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P10" t="str">
+      <c r="H9" t="str">
+        <v>-</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P9" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="Q9" t="str">
         <v>잠원동 27-2</v>
       </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str" xml:space="preserve">
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str" xml:space="preserve">
         <v xml:space="preserve">이디아커피 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
+      <c r="T9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C11" t="str">
+      <c r="B10" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C10" t="str">
         <v>25-서초구-10</v>
       </c>
-      <c r="D11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E11" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="D10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E10" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G10" t="str">
         <v>2</v>
       </c>
-      <c r="H11" t="str">
-        <v>-</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
+      <c r="H10" t="str">
+        <v>-</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
         <v>잠원동 27-8</v>
       </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str" xml:space="preserve">
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str" xml:space="preserve">
         <v xml:space="preserve">하나은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
+      <c r="T10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C12" t="str">
+      <c r="B11" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C11" t="str">
         <v>25-서초구-11</v>
       </c>
-      <c r="D12" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E12" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F12" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="D11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E11" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G11" t="str">
         <v>2</v>
       </c>
-      <c r="H12" t="str">
-        <v>-</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P12" t="str">
+      <c r="H11" t="str">
+        <v>-</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P11" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="Q11" t="str">
         <v>잠원동 28-1</v>
       </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str" xml:space="preserve">
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str" xml:space="preserve">
         <v xml:space="preserve">페페신사 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13">
+      <c r="T11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C13" t="str">
+      <c r="B12" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C12" t="str">
         <v>25-서초구-12</v>
       </c>
-      <c r="D13" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E13" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F13" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G13" t="str">
+      <c r="D12" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E12" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F12" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G12" t="str">
         <v>2</v>
       </c>
-      <c r="H13" t="str">
-        <v>-</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
-      <c r="O13" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P13" t="str">
+      <c r="H12" t="str">
+        <v>-</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P12" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="Q12" t="str">
         <v>잠원동 28-10</v>
       </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str" xml:space="preserve">
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str" xml:space="preserve">
         <v xml:space="preserve">HY빌딩 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
+      <c r="T12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C14" t="str">
+      <c r="B13" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C13" t="str">
         <v>25-서초구-13</v>
       </c>
-      <c r="D14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E14" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="D13" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E13" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F13" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G13" t="str">
         <v>2</v>
       </c>
-      <c r="H14" t="str">
-        <v>-</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>3</v>
-      </c>
-      <c r="O14" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P14" t="str">
+      <c r="H13" t="str">
+        <v>-</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P13" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="Q13" t="str">
         <v>잠원동 28-6</v>
       </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str" xml:space="preserve">
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str" xml:space="preserve">
         <v xml:space="preserve">현장(잠원동28-6) 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
+      <c r="T13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C15" t="str">
+      <c r="B14" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C14" t="str">
         <v>25-서초구-14</v>
       </c>
-      <c r="D15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E15" t="str">
-        <v>-</v>
-      </c>
-      <c r="F15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="D14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E14" t="str">
+        <v>-</v>
+      </c>
+      <c r="F14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G14" t="str">
         <v>2</v>
       </c>
-      <c r="H15" t="str">
-        <v>-</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P15" t="str">
+      <c r="H14" t="str">
+        <v>-</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P14" t="str">
         <v>보도침하(5cm)</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="Q14" t="str">
         <v>잠원동 28-6</v>
       </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str" xml:space="preserve">
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str" xml:space="preserve">
         <v xml:space="preserve">현장(잠원동28-6) 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16">
+      <c r="T14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C16" t="str">
+      <c r="B15" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C15" t="str">
         <v>25-서초구-15</v>
       </c>
-      <c r="D16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E16" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="D15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E15" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G15" t="str">
         <v>2</v>
       </c>
-      <c r="H16" t="str">
-        <v>-</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-      <c r="O16" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
+      <c r="H15" t="str">
+        <v>-</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v>잠원동 36-14</v>
       </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str" xml:space="preserve">
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str" xml:space="preserve">
         <v xml:space="preserve">KDB산업은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17">
+      <c r="T15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C17" t="str">
+      <c r="B16" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C16" t="str">
         <v>25-서초구-16</v>
       </c>
-      <c r="D17" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E17" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F17" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G17" t="str">
+      <c r="D16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E16" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G16" t="str">
         <v>2</v>
       </c>
-      <c r="H17" t="str">
-        <v>-</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>3</v>
-      </c>
-      <c r="O17" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
+      <c r="H16" t="str">
+        <v>-</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>잠원동 37-1</v>
       </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str" xml:space="preserve">
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str" xml:space="preserve">
         <v xml:space="preserve">ok광생약국 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C17" t="str">
+        <v>25-서초구-17</v>
+      </c>
+      <c r="D17" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E17" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F17" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2</v>
+      </c>
+      <c r="H17" t="str">
+        <v>-</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P17" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>논현역교차로</v>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str" xml:space="preserve">
+        <v xml:space="preserve">논현역 교차로_x000d_
+(강남대로)</v>
+      </c>
       <c r="T17" t="str">
         <v/>
       </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1363,1509 +1362,1508 @@
         <v>일반</v>
       </c>
       <c r="P18" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q18" t="str">
-        <v>논현역교차로</v>
+        <v>반포동 706-10</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str" xml:space="preserve">
-        <v xml:space="preserve">논현역 교차로_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C19" t="str">
-        <v>25-서초구-18</v>
-      </c>
-      <c r="D19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E19" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G19" t="str">
-        <v>2</v>
-      </c>
-      <c r="H19" t="str">
-        <v>-</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
-      <c r="O19" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v>반포동 706-10</v>
-      </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 #5번출 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20">
+      <c r="T18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C20" t="str">
+      <c r="B19" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C19" t="str">
         <v>25-서초구-19</v>
       </c>
-      <c r="D20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E20" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="D19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E19" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G19" t="str">
         <v>2</v>
       </c>
-      <c r="H20" t="str">
-        <v>-</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>3</v>
-      </c>
-      <c r="O20" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-      <c r="Q20" t="str">
+      <c r="H19" t="str">
+        <v>-</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>반포동 707-5</v>
       </c>
-      <c r="R20" t="str">
-        <v/>
-      </c>
-      <c r="S20" t="str" xml:space="preserve">
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 E/V_2호기 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21">
+      <c r="T19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C21" t="str">
+      <c r="B20" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C20" t="str">
         <v>25-서초구-20</v>
       </c>
-      <c r="D21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E21" t="str">
+      <c r="D20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E20" t="str">
         <v>종균열</v>
       </c>
-      <c r="F21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="F20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G20" t="str">
         <v>2</v>
       </c>
-      <c r="H21" t="str">
-        <v>-</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="H20" t="str">
+        <v>-</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <v>1</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>1</v>
       </c>
-      <c r="O21" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
+      <c r="O20" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v>반포동 707-11</v>
       </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str" xml:space="preserve">
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 #4번출구 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22">
+      <c r="T20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C22" t="str">
+      <c r="B21" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C21" t="str">
         <v>25-서초구-21</v>
       </c>
-      <c r="D22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E22" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="D21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E21" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G21" t="str">
         <v>2</v>
       </c>
-      <c r="H22" t="str">
-        <v>-</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
-      <c r="O22" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
+      <c r="H21" t="str">
+        <v>-</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v>반포동 722-20</v>
       </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str" xml:space="preserve">
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str" xml:space="preserve">
         <v xml:space="preserve">참치 앤 쿡 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23">
+      <c r="T21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C23" t="str">
+      <c r="B22" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C22" t="str">
         <v>25-서초구-22</v>
       </c>
-      <c r="D23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E23" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="D22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E22" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G22" t="str">
         <v>2</v>
       </c>
-      <c r="H23" t="str">
-        <v>-</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>3</v>
-      </c>
-      <c r="O23" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
+      <c r="H22" t="str">
+        <v>-</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
         <v>반포동 723-1</v>
       </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str" xml:space="preserve">
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str" xml:space="preserve">
         <v xml:space="preserve">뮬리성형외과 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24">
+      <c r="T22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C24" t="str">
+      <c r="B23" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C23" t="str">
         <v>25-서초구-23</v>
       </c>
-      <c r="D24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E24" t="str">
-        <v>-</v>
-      </c>
-      <c r="F24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G24" t="str">
+      <c r="D23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E23" t="str">
+        <v>-</v>
+      </c>
+      <c r="F23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G23" t="str">
         <v>2</v>
       </c>
-      <c r="H24" t="str">
-        <v>-</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P24" t="str">
+      <c r="H23" t="str">
+        <v>-</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P23" t="str">
         <v>보도침하</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="Q23" t="str">
         <v>반포동 736-2</v>
       </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str" xml:space="preserve">
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str" xml:space="preserve">
         <v xml:space="preserve">강남성모원 안과의원 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25">
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C25" t="str">
+      <c r="B24" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C24" t="str">
         <v>25-서초구-24</v>
       </c>
-      <c r="D25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E25" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="D24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E24" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G24" t="str">
         <v>2</v>
       </c>
-      <c r="H25" t="str">
-        <v>-</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>3</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>3</v>
-      </c>
-      <c r="O25" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
+      <c r="H24" t="str">
+        <v>-</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
         <v>반포동 736-17</v>
       </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str" xml:space="preserve">
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str" xml:space="preserve">
         <v xml:space="preserve">커피빈 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26">
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C26" t="str">
+      <c r="B25" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C25" t="str">
         <v>25-서초구-25</v>
       </c>
-      <c r="D26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E26" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="D25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E25" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G25" t="str">
         <v>2</v>
       </c>
-      <c r="H26" t="str">
-        <v>-</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>3</v>
-      </c>
-      <c r="O26" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
+      <c r="H25" t="str">
+        <v>-</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
         <v>반포동 736-17</v>
       </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str" xml:space="preserve">
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str" xml:space="preserve">
         <v xml:space="preserve">스타벅스 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27">
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C27" t="str">
+      <c r="B26" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C26" t="str">
         <v>25-서초구-26</v>
       </c>
-      <c r="D27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E27" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G27" t="str">
+      <c r="D26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E26" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G26" t="str">
         <v>2</v>
       </c>
-      <c r="H27" t="str">
-        <v>-</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>3</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>3</v>
-      </c>
-      <c r="O27" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
+      <c r="H26" t="str">
+        <v>-</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v>서초동 1303-43</v>
       </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str" xml:space="preserve">
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str" xml:space="preserve">
         <v xml:space="preserve">신논현역 교차로_x000d_
 =교보타워 교차로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28">
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C28" t="str">
+      <c r="B27" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C27" t="str">
         <v>25-서초구-27</v>
       </c>
-      <c r="D28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E28" t="str">
+      <c r="D27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E27" t="str">
         <v>종균열</v>
       </c>
-      <c r="F28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G28" t="str">
+      <c r="F27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G27" t="str">
         <v>2</v>
       </c>
-      <c r="H28" t="str">
-        <v>-</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
+      <c r="H27" t="str">
+        <v>-</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>1</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>1</v>
       </c>
-      <c r="O28" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
+      <c r="O27" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v>서초동 1303-22</v>
       </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28" t="str" xml:space="preserve">
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str" xml:space="preserve">
         <v xml:space="preserve">교보타워 주차장 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29">
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C29" t="str">
+      <c r="B28" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C28" t="str">
         <v>25-서초구-28</v>
       </c>
-      <c r="D29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E29" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G29" t="str">
+      <c r="D28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E28" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G28" t="str">
         <v>2</v>
       </c>
-      <c r="H29" t="str">
-        <v>-</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>3</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P29" t="str">
-        <v/>
-      </c>
-      <c r="Q29" t="str">
+      <c r="H28" t="str">
+        <v>-</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v>서초동 1303-35</v>
       </c>
-      <c r="R29" t="str">
-        <v/>
-      </c>
-      <c r="S29" t="str" xml:space="preserve">
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str" xml:space="preserve">
         <v xml:space="preserve">던킹도너츠 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30">
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C30" t="str">
+      <c r="B29" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C29" t="str">
         <v>25-서초구-29</v>
       </c>
-      <c r="D30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E30" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G30" t="str">
+      <c r="D29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E29" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G29" t="str">
         <v>2</v>
       </c>
-      <c r="H30" t="str">
-        <v>-</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>3</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-      <c r="O30" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P30" t="str">
-        <v/>
-      </c>
-      <c r="Q30" t="str">
+      <c r="H29" t="str">
+        <v>-</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
         <v>서초동 1304-2</v>
       </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str" xml:space="preserve">
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str" xml:space="preserve">
         <v xml:space="preserve">수세연 안과의원_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31">
+      <c r="T29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C31" t="str">
+      <c r="B30" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C30" t="str">
         <v>25-서초구-30</v>
       </c>
-      <c r="D31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E31" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G31" t="str">
+      <c r="D30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E30" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G30" t="str">
         <v>2</v>
       </c>
-      <c r="H31" t="str">
-        <v>-</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
-      <c r="O31" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P31" t="str">
+      <c r="H30" t="str">
+        <v>-</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P30" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="Q30" t="str">
         <v>서초동 1304-3</v>
       </c>
-      <c r="R31" t="str">
-        <v/>
-      </c>
-      <c r="S31" t="str" xml:space="preserve">
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str" xml:space="preserve">
         <v xml:space="preserve">자라 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32">
+      <c r="T30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C32" t="str">
+      <c r="B31" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C31" t="str">
         <v>25-서초구-31</v>
       </c>
-      <c r="D32" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E32" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F32" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G32" t="str">
+      <c r="D31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E31" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G31" t="str">
         <v>2</v>
       </c>
-      <c r="H32" t="str">
-        <v>-</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>3</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-      <c r="O32" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P32" t="str">
+      <c r="H31" t="str">
+        <v>-</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="O31" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P31" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="Q31" t="str">
         <v>서초동 1305</v>
       </c>
-      <c r="R32" t="str">
-        <v/>
-      </c>
-      <c r="S32" t="str" xml:space="preserve">
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str" xml:space="preserve">
         <v xml:space="preserve">준오헤어 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33">
+      <c r="T31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C33" t="str">
+      <c r="B32" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C32" t="str">
         <v>25-서초구-32</v>
       </c>
-      <c r="D33" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E33" t="str">
-        <v>-</v>
-      </c>
-      <c r="F33" t="str">
-        <v>-</v>
-      </c>
-      <c r="G33" t="str">
+      <c r="D32" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E32" t="str">
+        <v>-</v>
+      </c>
+      <c r="F32" t="str">
+        <v>-</v>
+      </c>
+      <c r="G32" t="str">
         <v>2</v>
       </c>
-      <c r="H33" t="str">
-        <v>-</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P33" t="str">
+      <c r="H32" t="str">
+        <v>-</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P32" t="str">
         <v>보도침하</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="Q32" t="str">
         <v>서초동 1305</v>
       </c>
-      <c r="R33" t="str">
-        <v/>
-      </c>
-      <c r="S33" t="str" xml:space="preserve">
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str" xml:space="preserve">
         <v xml:space="preserve">준오헤어 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34">
+      <c r="T32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C34" t="str">
+      <c r="B33" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C33" t="str">
         <v>25-서초구-33</v>
       </c>
-      <c r="D34" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E34" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F34" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G34" t="str">
+      <c r="D33" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E33" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F33" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G33" t="str">
         <v>2</v>
       </c>
-      <c r="H34" t="str">
-        <v>-</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>3</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>3</v>
-      </c>
-      <c r="O34" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P34" t="str">
-        <v/>
-      </c>
-      <c r="Q34" t="str">
+      <c r="H33" t="str">
+        <v>-</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
         <v>서초동 1305-2</v>
       </c>
-      <c r="R34" t="str">
-        <v/>
-      </c>
-      <c r="S34" t="str" xml:space="preserve">
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str" xml:space="preserve">
         <v xml:space="preserve">라인프렌즈 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35">
+      <c r="T33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C35" t="str">
+      <c r="B34" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C34" t="str">
         <v>25-서초구-34</v>
       </c>
-      <c r="D35" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E35" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F35" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G35" t="str">
+      <c r="D34" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E34" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F34" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G34" t="str">
         <v>2</v>
       </c>
-      <c r="H35" t="str">
-        <v>-</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>3</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>3</v>
-      </c>
-      <c r="O35" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P35" t="str">
-        <v/>
-      </c>
-      <c r="Q35" t="str">
+      <c r="H34" t="str">
+        <v>-</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
         <v>서초동 1305-7</v>
       </c>
-      <c r="R35" t="str">
-        <v/>
-      </c>
-      <c r="S35" t="str" xml:space="preserve">
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str" xml:space="preserve">
         <v xml:space="preserve">올리브영 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36">
+      <c r="T34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C36" t="str">
+      <c r="B35" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C35" t="str">
         <v>25-서초구-35</v>
       </c>
-      <c r="D36" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E36" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F36" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G36" t="str">
+      <c r="D35" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E35" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F35" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G35" t="str">
         <v>2</v>
       </c>
-      <c r="H36" t="str">
-        <v>-</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>3</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P36" t="str">
-        <v/>
-      </c>
-      <c r="Q36" t="str">
+      <c r="H35" t="str">
+        <v>-</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="O35" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
         <v>서초동 1306</v>
       </c>
-      <c r="R36" t="str">
-        <v/>
-      </c>
-      <c r="S36" t="str" xml:space="preserve">
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str" xml:space="preserve">
         <v xml:space="preserve">비엠사오 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37">
+      <c r="T35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C37" t="str">
+      <c r="B36" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C36" t="str">
         <v>25-서초구-36</v>
       </c>
-      <c r="D37" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E37" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F37" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G37" t="str">
+      <c r="D36" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E36" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F36" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G36" t="str">
         <v>2</v>
       </c>
-      <c r="H37" t="str">
-        <v>-</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>3</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>3</v>
-      </c>
-      <c r="O37" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P37" t="str">
-        <v/>
-      </c>
-      <c r="Q37" t="str">
+      <c r="H36" t="str">
+        <v>-</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
         <v>서초동 1306-2</v>
       </c>
-      <c r="R37" t="str">
-        <v/>
-      </c>
-      <c r="S37" t="str" xml:space="preserve">
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str" xml:space="preserve">
         <v xml:space="preserve">ABC마트 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38">
+      <c r="T36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C38" t="str">
+      <c r="B37" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C37" t="str">
         <v>25-서초구-37</v>
       </c>
-      <c r="D38" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E38" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F38" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G38" t="str">
+      <c r="D37" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E37" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F37" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G37" t="str">
         <v>2</v>
       </c>
-      <c r="H38" t="str">
-        <v>-</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>3</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>3</v>
-      </c>
-      <c r="O38" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P38" t="str">
-        <v/>
-      </c>
-      <c r="Q38" t="str">
+      <c r="H37" t="str">
+        <v>-</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
         <v>서초동 1306-8</v>
       </c>
-      <c r="R38" t="str">
-        <v/>
-      </c>
-      <c r="S38" t="str" xml:space="preserve">
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str" xml:space="preserve">
         <v xml:space="preserve">강남 성모안과 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39">
+      <c r="T37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C39" t="str">
+      <c r="B38" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C38" t="str">
         <v>25-서초구-38</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D38" t="str">
         <v>보통</v>
       </c>
-      <c r="E39" t="str">
-        <v>-</v>
-      </c>
-      <c r="F39" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G39" t="str">
+      <c r="E38" t="str">
+        <v>-</v>
+      </c>
+      <c r="F38" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G38" t="str">
         <v>2</v>
       </c>
-      <c r="H39" t="str">
-        <v>-</v>
-      </c>
-      <c r="I39">
-        <v>3</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>3</v>
-      </c>
-      <c r="O39" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P39" t="str">
+      <c r="H38" t="str">
+        <v>-</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P38" t="str">
         <v>5cm이상 침하</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="Q38" t="str">
         <v>서초동 1306-8</v>
       </c>
-      <c r="R39" t="str">
-        <v/>
-      </c>
-      <c r="S39" t="str" xml:space="preserve">
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str" xml:space="preserve">
         <v xml:space="preserve">강남 성모안과 앞_x000d_
 횡단보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40">
+      <c r="T38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C40" t="str">
+      <c r="B39" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C39" t="str">
         <v>25-서초구-39</v>
       </c>
-      <c r="D40" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E40" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F40" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G40" t="str">
+      <c r="D39" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E39" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F39" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G39" t="str">
         <v>2</v>
       </c>
-      <c r="H40" t="str">
-        <v>-</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>3</v>
-      </c>
-      <c r="O40" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
-      <c r="Q40" t="str">
+      <c r="H39" t="str">
+        <v>-</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>3</v>
+      </c>
+      <c r="O39" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
         <v>서초동 1318</v>
       </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str" xml:space="preserve">
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str" xml:space="preserve">
         <v xml:space="preserve">삼성스토어 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41">
+      <c r="T39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C41" t="str">
+      <c r="B40" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C40" t="str">
         <v>25-서초구-40</v>
       </c>
-      <c r="D41" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E41" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F41" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G41" t="str">
+      <c r="D40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E40" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G40" t="str">
         <v>2</v>
       </c>
-      <c r="H41" t="str">
-        <v>-</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>3</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>3</v>
-      </c>
-      <c r="O41" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P41" t="str">
+      <c r="H40" t="str">
+        <v>-</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
+      <c r="O40" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P40" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q41" t="str">
+      <c r="Q40" t="str">
         <v>서초동 1318-2</v>
       </c>
-      <c r="R41" t="str">
-        <v/>
-      </c>
-      <c r="S41" t="str" xml:space="preserve">
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str" xml:space="preserve">
         <v xml:space="preserve">하나은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>26-1</v>
+      </c>
+      <c r="B41" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C41" t="str">
+        <v>26-서초구-01</v>
+      </c>
+      <c r="D41" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E41" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F41" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G41" t="str">
+        <v>3</v>
+      </c>
+      <c r="H41" t="str">
+        <v>-</v>
+      </c>
+      <c r="I41" t="str">
+        <v>0</v>
+      </c>
+      <c r="J41" t="str">
+        <v>0</v>
+      </c>
+      <c r="K41" t="str">
+        <v>0</v>
+      </c>
+      <c r="L41" t="str">
+        <v>0</v>
+      </c>
+      <c r="M41" t="str">
+        <v>0</v>
+      </c>
+      <c r="N41" t="str">
+        <v>0</v>
+      </c>
+      <c r="O41" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P41" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>잠원동12-21</v>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v>꿉당 앞 도로(강남대로615)</v>
+      </c>
       <c r="T41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-1</v>
+        <v>26-2</v>
       </c>
       <c r="B42" t="str">
         <v>강남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F42" t="str">
         <v>양호</v>
@@ -2880,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" t="str">
         <v>0</v>
@@ -2892,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
@@ -2901,13 +2899,13 @@
         <v>5cm미만 침하</v>
       </c>
       <c r="Q42" t="str">
-        <v>잠원동12-21</v>
+        <v>잠원동12-22</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>꿉당 앞 도로(강남대로615)</v>
+        <v>성락빌딩 앞 횡단보도(강남대로613)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2915,19 +2913,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-2</v>
+        <v>26-3</v>
       </c>
       <c r="B43" t="str">
         <v>강남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F43" t="str">
         <v>양호</v>
@@ -2942,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43" t="str">
         <v>0</v>
@@ -2954,22 +2952,22 @@
         <v>0</v>
       </c>
       <c r="N43" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q43" t="str">
-        <v>잠원동12-22</v>
+        <v>잠원동13-6</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>성락빌딩 앞 횡단보도(강남대로613)</v>
+        <v>GS칼텍스 직역 남서울주유소 앞 교차로(나루터로83)</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2977,19 +2975,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-3</v>
+        <v>26-4</v>
       </c>
       <c r="B44" t="str">
         <v>강남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>종,횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F44" t="str">
         <v>양호</v>
@@ -3004,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" t="str">
         <v>0</v>
@@ -3016,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
@@ -3025,13 +3023,13 @@
         <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>잠원동13-6</v>
+        <v>잠원동20-9</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>GS칼텍스 직역 남서울주유소 앞 교차로(나루터로83)</v>
+        <v>휴먼타워 앞 신사역 교차로(강남대로605)</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -3039,19 +3037,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-4</v>
+        <v>26-5</v>
       </c>
       <c r="B45" t="str">
         <v>강남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -3066,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45" t="str">
         <v>0</v>
@@ -3078,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
@@ -3087,13 +3085,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>잠원동20-9</v>
+        <v>잠원동20-5</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>휴먼타워 앞 신사역 교차로(강남대로605)</v>
+        <v>인성빌딩 파리바게트 앞 횡단보도(강남대로603)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3101,19 +3099,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-5</v>
+        <v>26-6</v>
       </c>
       <c r="B46" t="str">
         <v>강남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3128,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" t="str">
         <v>0</v>
@@ -3140,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
@@ -3149,13 +3147,13 @@
         <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>잠원동20-5</v>
+        <v>잠원동21-3</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>인성빌딩 파리바게트 앞 횡단보도(강남대로603)</v>
+        <v>진미선빌딩 앞 도로(강남대로597)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3163,19 +3161,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-6</v>
+        <v>26-7</v>
       </c>
       <c r="B47" t="str">
         <v>강남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3190,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3208,7 +3206,7 @@
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q47" t="str">
         <v>잠원동21-3</v>
@@ -3217,7 +3215,7 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>진미선빌딩 앞 도로(강남대로597)</v>
+        <v>버스전용차선(강남대로597)</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3225,19 +3223,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-7</v>
+        <v>26-8</v>
       </c>
       <c r="B48" t="str">
         <v>강남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>양호</v>
+        <v>거북동</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3252,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3264,22 +3262,22 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q48" t="str">
-        <v>잠원동21-3</v>
+        <v>잠원동27-2</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>버스전용차선(강남대로597)</v>
+        <v>메디칼타워 올리브영 앞 도로(강남대로589)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3287,19 +3285,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-8</v>
+        <v>26-9</v>
       </c>
       <c r="B49" t="str">
         <v>강남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>거북동</v>
+        <v>거북등</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3332,16 +3330,16 @@
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q49" t="str">
-        <v>잠원동27-2</v>
+        <v>잠원동27-8</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>메디칼타워 올리브영 앞 도로(강남대로589)</v>
+        <v>KCC건설 앞 도로(강남대로587)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3349,13 +3347,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-9</v>
+        <v>26-10</v>
       </c>
       <c r="B50" t="str">
         <v>강남대로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3394,16 +3392,16 @@
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>잠원동27-8</v>
+        <v>잠원동28-10</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>KCC건설 앞 도로(강남대로587)</v>
+        <v>HY빌딩 앞 도로(강남대로577)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3411,13 +3409,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B51" t="str">
         <v>강남대로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3459,13 +3457,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>잠원동28-10</v>
+        <v>잠원동28-6</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>HY빌딩 앞 도로(강남대로577)</v>
+        <v>인접공사현장 앞 도로(강남대로573)</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3473,13 +3471,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B52" t="str">
         <v>강남대로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3521,13 +3519,13 @@
         <v>-</v>
       </c>
       <c r="Q52" t="str">
-        <v>잠원동28-6</v>
+        <v>잠원동36-13</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>인접공사현장 앞 도로(강남대로573)</v>
+        <v>더뉴치과의원 앞 도로(강남대로567)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3535,19 +3533,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B53" t="str">
         <v>강남대로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
       </c>
       <c r="E53" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F53" t="str">
         <v>양호</v>
@@ -3562,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="str">
         <v>0</v>
@@ -3574,13 +3572,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O53" t="str">
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q53" t="str">
         <v>잠원동36-13</v>
@@ -3589,7 +3587,7 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>더뉴치과의원 앞 도로(강남대로567)</v>
+        <v>버스전용차선 (강남대로567)</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3597,19 +3595,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B54" t="str">
         <v>강남대로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
       </c>
       <c r="E54" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F54" t="str">
         <v>양호</v>
@@ -3624,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54" t="str">
         <v>0</v>
@@ -3636,22 +3634,22 @@
         <v>0</v>
       </c>
       <c r="N54" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O54" t="str">
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q54" t="str">
-        <v>잠원동36-13</v>
+        <v>잠원동37-6</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>버스전용차선 (강남대로567)</v>
+        <v>정인빌딩 광주은행 앞 도로(강남대로559)</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3659,13 +3657,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B55" t="str">
         <v>강남대로</v>
       </c>
       <c r="C55" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3704,16 +3702,16 @@
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q55" t="str">
-        <v>잠원동37-6</v>
+        <v>논현역교차로</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>정인빌딩 광주은행 앞 도로(강남대로559)</v>
+        <v>논현역 교차로(학동로102)</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3721,13 +3719,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B56" t="str">
         <v>강남대로</v>
       </c>
       <c r="C56" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3766,16 +3764,16 @@
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q56" t="str">
-        <v>논현역교차로</v>
+        <v>반포동706-10</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>논현역 교차로(학동로102)</v>
+        <v>논현역 #5출구 앞 횡단보도(강남대로545-4)</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3783,13 +3781,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B57" t="str">
         <v>강남대로</v>
       </c>
       <c r="C57" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3831,13 +3829,13 @@
         <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>반포동706-10</v>
+        <v>반포동707-11</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>논현역 #5출구 앞 횡단보도(강남대로545-4)</v>
+        <v>프린스빌딩 서브웨이 앞(강남대로535)</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3845,13 +3843,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B58" t="str">
         <v>강남대로</v>
       </c>
       <c r="C58" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3893,27 +3891,27 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>반포동707-11</v>
+        <v>반포동722-20</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>프린스빌딩 서브웨이 앞(강남대로535)</v>
+        <v>브랜드칸타워 투썸플레이스 앞(강남대로527)</v>
       </c>
       <c r="T58" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B59" t="str">
         <v>강남대로</v>
       </c>
       <c r="C59" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3955,13 +3953,13 @@
         <v>-</v>
       </c>
       <c r="Q59" t="str">
-        <v>반포동722-20</v>
+        <v>반포동722-31</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>브랜드칸타워 투썸플레이스 앞(강남대로527)</v>
+        <v>성창빌딩 메가커피 앞 횡단보도(강남대로523)</v>
       </c>
       <c r="T59" t="str">
         <v>현장확인필요</v>
@@ -3969,13 +3967,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B60" t="str">
         <v>강남대로</v>
       </c>
       <c r="C60" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -4014,16 +4012,16 @@
         <v>일반</v>
       </c>
       <c r="P60" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q60" t="str">
-        <v>반포동722-31</v>
+        <v>반포동722-38</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>성창빌딩 메가커피 앞 횡단보도(강남대로523)</v>
+        <v>태영빌딩 올리브약국 앞(강남대로521-4)</v>
       </c>
       <c r="T60" t="str">
         <v>현장확인필요</v>
@@ -4031,13 +4029,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B61" t="str">
         <v>강남대로</v>
       </c>
       <c r="C61" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4076,16 +4074,16 @@
         <v>일반</v>
       </c>
       <c r="P61" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q61" t="str">
-        <v>반포동722-38</v>
+        <v>반포동723-22</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>태영빌딩 올리브약국 앞(강남대로521-4)</v>
+        <v>하늘안과 앞 (강남대로509)</v>
       </c>
       <c r="T61" t="str">
         <v>현장확인필요</v>
@@ -4093,13 +4091,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B62" t="str">
         <v>강남대로</v>
       </c>
       <c r="C62" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4141,13 +4139,13 @@
         <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>반포동723-22</v>
+        <v>반포동736-17</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>하늘안과 앞 (강남대로509)</v>
+        <v>청하빌딩 커피빈 앞(강남대로503)</v>
       </c>
       <c r="T62" t="str">
         <v>현장확인필요</v>
@@ -4155,13 +4153,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B63" t="str">
         <v>강남대로</v>
       </c>
       <c r="C63" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4203,13 +4201,13 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>반포동736-17</v>
+        <v>반포동737-19</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>청하빌딩 커피빈 앞(강남대로503)</v>
+        <v>철거현장(강남대로79길2)</v>
       </c>
       <c r="T63" t="str">
         <v>현장확인필요</v>
@@ -4217,13 +4215,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B64" t="str">
         <v>강남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4265,13 +4263,13 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>반포동737-19</v>
+        <v>반포동748-6</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>철거현장(강남대로79길2)</v>
+        <v>페이지랩의원 앞(강남대로477)</v>
       </c>
       <c r="T64" t="str">
         <v>현장확인필요</v>
@@ -4279,13 +4277,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B65" t="str">
         <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4327,13 +4325,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>반포동748-6</v>
+        <v>교보타워사거리</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>페이지랩의원 앞(강남대로477)</v>
+        <v>신논현역 교차로 횡단보도(봉은사로102)</v>
       </c>
       <c r="T65" t="str">
         <v>현장확인필요</v>
@@ -4341,13 +4339,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4386,16 +4384,16 @@
         <v>일반</v>
       </c>
       <c r="P66" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q66" t="str">
-        <v>교보타워사거리</v>
+        <v>서초동1303-37</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>신논현역 교차로 횡단보도(봉은사로102)</v>
+        <v>w타워 하이디라오 앞(서초대로77길54)</v>
       </c>
       <c r="T66" t="str">
         <v>현장확인필요</v>

--- a/25-새서울철도-서초구-보고서.xlsx
+++ b/25-새서울철도-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,19 +485,19 @@
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
       </c>
       <c r="E5" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F5" t="str">
         <v>양호</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -524,743 +524,742 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="str">
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>보도침하</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q5" t="str">
-        <v>잠원동 21-2</v>
+        <v>잠원동 21-3</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str" xml:space="preserve">
-        <v xml:space="preserve">CELL TRION 앞_x000d_
-보도_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C6" t="str">
-        <v>25-서초구-6</v>
-      </c>
-      <c r="D6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E6" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2</v>
-      </c>
-      <c r="H6" t="str">
-        <v>-</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>3</v>
-      </c>
-      <c r="O6" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P6" t="str">
-        <v>5cm미만 침하</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>잠원동 21-3</v>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">서울미소그린치과 앞_x000d_
 버스정류장_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B7" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="B6" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C6" t="str">
         <v>25-서초구-7</v>
       </c>
-      <c r="D7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E7" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="D6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E6" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G6" t="str">
         <v>2</v>
       </c>
-      <c r="H7" t="str">
-        <v>-</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
-      <c r="O7" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P7" t="str">
+      <c r="H6" t="str">
+        <v>-</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P6" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="Q6" t="str">
         <v>잠원동 21-3</v>
       </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str" xml:space="preserve">
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">씨티약국 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
+      <c r="T6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
         <v>8</v>
       </c>
-      <c r="B8" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="B7" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C7" t="str">
         <v>25-서초구-8</v>
       </c>
-      <c r="D8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E8" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="D7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E7" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G7" t="str">
         <v>2</v>
       </c>
-      <c r="H8" t="str">
-        <v>-</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-      <c r="O8" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P8" t="str">
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P7" t="str">
         <v>버스차선 확인불가</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q7" t="str">
         <v>잠원동 21-7</v>
       </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str" xml:space="preserve">
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str" xml:space="preserve">
         <v xml:space="preserve">스타벅스 앞_x000d_
 버스차선_x000d_
 (강남대로)</v>
       </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
         <v>9</v>
       </c>
-      <c r="B9" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B8" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C8" t="str">
         <v>25-서초구-9</v>
       </c>
-      <c r="D9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E9" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="D8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E8" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G8" t="str">
         <v>2</v>
       </c>
-      <c r="H9" t="str">
-        <v>-</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P9" t="str">
+      <c r="H8" t="str">
+        <v>-</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P8" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="Q8" t="str">
         <v>잠원동 27-2</v>
       </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str" xml:space="preserve">
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str" xml:space="preserve">
         <v xml:space="preserve">이디아커피 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
+      <c r="T8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
         <v>10</v>
       </c>
-      <c r="B10" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C10" t="str">
+      <c r="B9" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C9" t="str">
         <v>25-서초구-10</v>
       </c>
-      <c r="D10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E10" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="D9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E9" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G9" t="str">
         <v>2</v>
       </c>
-      <c r="H10" t="str">
-        <v>-</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
-      <c r="O10" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
+      <c r="H9" t="str">
+        <v>-</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
         <v>잠원동 27-8</v>
       </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str" xml:space="preserve">
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str" xml:space="preserve">
         <v xml:space="preserve">하나은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
+      <c r="T9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
         <v>11</v>
       </c>
-      <c r="B11" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C11" t="str">
+      <c r="B10" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C10" t="str">
         <v>25-서초구-11</v>
       </c>
-      <c r="D11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E11" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="D10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E10" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G10" t="str">
         <v>2</v>
       </c>
-      <c r="H11" t="str">
-        <v>-</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P11" t="str">
+      <c r="H10" t="str">
+        <v>-</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P10" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="Q10" t="str">
         <v>잠원동 28-1</v>
       </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str" xml:space="preserve">
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str" xml:space="preserve">
         <v xml:space="preserve">페페신사 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
+      <c r="T10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
         <v>12</v>
       </c>
-      <c r="B12" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C12" t="str">
+      <c r="B11" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C11" t="str">
         <v>25-서초구-12</v>
       </c>
-      <c r="D12" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E12" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F12" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="D11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E11" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G11" t="str">
         <v>2</v>
       </c>
-      <c r="H12" t="str">
-        <v>-</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P12" t="str">
+      <c r="H11" t="str">
+        <v>-</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P11" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="Q11" t="str">
         <v>잠원동 28-10</v>
       </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str" xml:space="preserve">
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str" xml:space="preserve">
         <v xml:space="preserve">HY빌딩 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13">
+      <c r="T11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12">
         <v>13</v>
       </c>
-      <c r="B13" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C13" t="str">
+      <c r="B12" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C12" t="str">
         <v>25-서초구-13</v>
       </c>
-      <c r="D13" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E13" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F13" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G13" t="str">
+      <c r="D12" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E12" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F12" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G12" t="str">
         <v>2</v>
       </c>
-      <c r="H13" t="str">
-        <v>-</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
-      <c r="O13" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P13" t="str">
+      <c r="H12" t="str">
+        <v>-</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P12" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="Q12" t="str">
         <v>잠원동 28-6</v>
       </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str" xml:space="preserve">
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str" xml:space="preserve">
         <v xml:space="preserve">현장(잠원동28-6) 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
+      <c r="T12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13">
         <v>14</v>
       </c>
-      <c r="B14" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C14" t="str">
+      <c r="B13" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C13" t="str">
         <v>25-서초구-14</v>
       </c>
-      <c r="D14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E14" t="str">
-        <v>-</v>
-      </c>
-      <c r="F14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="D13" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E13" t="str">
+        <v>-</v>
+      </c>
+      <c r="F13" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G13" t="str">
         <v>2</v>
       </c>
-      <c r="H14" t="str">
-        <v>-</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P14" t="str">
+      <c r="H13" t="str">
+        <v>-</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P13" t="str">
         <v>보도침하(5cm)</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="Q13" t="str">
         <v>잠원동 28-6</v>
       </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str" xml:space="preserve">
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str" xml:space="preserve">
         <v xml:space="preserve">현장(잠원동28-6) 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
+      <c r="T13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
         <v>15</v>
       </c>
-      <c r="B15" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C15" t="str">
+      <c r="B14" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C14" t="str">
         <v>25-서초구-15</v>
       </c>
-      <c r="D15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E15" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="D14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E14" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G14" t="str">
         <v>2</v>
       </c>
-      <c r="H15" t="str">
-        <v>-</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>3</v>
-      </c>
-      <c r="O15" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
+      <c r="H14" t="str">
+        <v>-</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
         <v>잠원동 36-14</v>
       </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str" xml:space="preserve">
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str" xml:space="preserve">
         <v xml:space="preserve">KDB산업은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16">
+      <c r="T14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15">
         <v>16</v>
       </c>
-      <c r="B16" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C16" t="str">
+      <c r="B15" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C15" t="str">
         <v>25-서초구-16</v>
       </c>
-      <c r="D16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E16" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="D15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E15" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G15" t="str">
         <v>2</v>
       </c>
-      <c r="H16" t="str">
-        <v>-</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-      <c r="O16" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
+      <c r="H15" t="str">
+        <v>-</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v>잠원동 37-1</v>
       </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str" xml:space="preserve">
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str" xml:space="preserve">
         <v xml:space="preserve">ok광생약국 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C16" t="str">
+        <v>25-서초구-17</v>
+      </c>
+      <c r="D16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E16" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2</v>
+      </c>
+      <c r="H16" t="str">
+        <v>-</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P16" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>논현역교차로</v>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str" xml:space="preserve">
+        <v xml:space="preserve">논현역 교차로_x000d_
+(강남대로)</v>
+      </c>
       <c r="T16" t="str">
         <v/>
       </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1299,1509 +1298,1508 @@
         <v>일반</v>
       </c>
       <c r="P17" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
-        <v>논현역교차로</v>
+        <v>반포동 706-10</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str" xml:space="preserve">
-        <v xml:space="preserve">논현역 교차로_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C18" t="str">
-        <v>25-서초구-18</v>
-      </c>
-      <c r="D18" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E18" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F18" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G18" t="str">
-        <v>2</v>
-      </c>
-      <c r="H18" t="str">
-        <v>-</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>3</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>3</v>
-      </c>
-      <c r="O18" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <v>반포동 706-10</v>
-      </c>
-      <c r="R18" t="str">
-        <v/>
-      </c>
-      <c r="S18" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 #5번출 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19">
+      <c r="T17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18">
         <v>19</v>
       </c>
-      <c r="B19" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C19" t="str">
+      <c r="B18" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C18" t="str">
         <v>25-서초구-19</v>
       </c>
-      <c r="D19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E19" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G19" t="str">
+      <c r="D18" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E18" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F18" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G18" t="str">
         <v>2</v>
       </c>
-      <c r="H19" t="str">
-        <v>-</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
-      <c r="O19" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
+      <c r="H18" t="str">
+        <v>-</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v>반포동 707-5</v>
       </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str" xml:space="preserve">
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 E/V_2호기 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20">
+      <c r="T18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19">
         <v>20</v>
       </c>
-      <c r="B20" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C20" t="str">
+      <c r="B19" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C19" t="str">
         <v>25-서초구-20</v>
       </c>
-      <c r="D20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E20" t="str">
+      <c r="D19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E19" t="str">
         <v>종균열</v>
       </c>
-      <c r="F20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="F19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G19" t="str">
         <v>2</v>
       </c>
-      <c r="H20" t="str">
-        <v>-</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
+      <c r="H19" t="str">
+        <v>-</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>1</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="O20" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-      <c r="Q20" t="str">
+      <c r="O19" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>반포동 707-11</v>
       </c>
-      <c r="R20" t="str">
-        <v/>
-      </c>
-      <c r="S20" t="str" xml:space="preserve">
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 #4번출구 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21">
+      <c r="T19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20">
         <v>21</v>
       </c>
-      <c r="B21" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C21" t="str">
+      <c r="B20" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C20" t="str">
         <v>25-서초구-21</v>
       </c>
-      <c r="D21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E21" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="D20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E20" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G20" t="str">
         <v>2</v>
       </c>
-      <c r="H21" t="str">
-        <v>-</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>3</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>3</v>
-      </c>
-      <c r="O21" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
+      <c r="H20" t="str">
+        <v>-</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v>반포동 722-20</v>
       </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str" xml:space="preserve">
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str" xml:space="preserve">
         <v xml:space="preserve">참치 앤 쿡 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22">
+      <c r="T20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21">
         <v>22</v>
       </c>
-      <c r="B22" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C22" t="str">
+      <c r="B21" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C21" t="str">
         <v>25-서초구-22</v>
       </c>
-      <c r="D22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E22" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="D21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E21" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G21" t="str">
         <v>2</v>
       </c>
-      <c r="H22" t="str">
-        <v>-</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
-      <c r="O22" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
+      <c r="H21" t="str">
+        <v>-</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v>반포동 723-1</v>
       </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str" xml:space="preserve">
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str" xml:space="preserve">
         <v xml:space="preserve">뮬리성형외과 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23">
+      <c r="T21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
         <v>23</v>
       </c>
-      <c r="B23" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C23" t="str">
+      <c r="B22" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C22" t="str">
         <v>25-서초구-23</v>
       </c>
-      <c r="D23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E23" t="str">
-        <v>-</v>
-      </c>
-      <c r="F23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="D22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E22" t="str">
+        <v>-</v>
+      </c>
+      <c r="F22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G22" t="str">
         <v>2</v>
       </c>
-      <c r="H23" t="str">
-        <v>-</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P23" t="str">
+      <c r="H22" t="str">
+        <v>-</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P22" t="str">
         <v>보도침하</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="Q22" t="str">
         <v>반포동 736-2</v>
       </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str" xml:space="preserve">
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str" xml:space="preserve">
         <v xml:space="preserve">강남성모원 안과의원 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24">
+      <c r="T22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23">
         <v>24</v>
       </c>
-      <c r="B24" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C24" t="str">
+      <c r="B23" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C23" t="str">
         <v>25-서초구-24</v>
       </c>
-      <c r="D24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E24" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G24" t="str">
+      <c r="D23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E23" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G23" t="str">
         <v>2</v>
       </c>
-      <c r="H24" t="str">
-        <v>-</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
+      <c r="H23" t="str">
+        <v>-</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+      <c r="O23" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
         <v>반포동 736-17</v>
       </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str" xml:space="preserve">
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str" xml:space="preserve">
         <v xml:space="preserve">커피빈 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25">
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24">
         <v>25</v>
       </c>
-      <c r="B25" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C25" t="str">
+      <c r="B24" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C24" t="str">
         <v>25-서초구-25</v>
       </c>
-      <c r="D25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E25" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="D24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E24" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G24" t="str">
         <v>2</v>
       </c>
-      <c r="H25" t="str">
-        <v>-</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>3</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>3</v>
-      </c>
-      <c r="O25" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
+      <c r="H24" t="str">
+        <v>-</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
         <v>반포동 736-17</v>
       </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str" xml:space="preserve">
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str" xml:space="preserve">
         <v xml:space="preserve">스타벅스 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26">
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25">
         <v>26</v>
       </c>
-      <c r="B26" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C26" t="str">
+      <c r="B25" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C25" t="str">
         <v>25-서초구-26</v>
       </c>
-      <c r="D26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E26" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="D25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E25" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G25" t="str">
         <v>2</v>
       </c>
-      <c r="H26" t="str">
-        <v>-</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>3</v>
-      </c>
-      <c r="O26" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
+      <c r="H25" t="str">
+        <v>-</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
         <v>서초동 1303-43</v>
       </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str" xml:space="preserve">
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str" xml:space="preserve">
         <v xml:space="preserve">신논현역 교차로_x000d_
 =교보타워 교차로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27">
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26">
         <v>27</v>
       </c>
-      <c r="B27" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C27" t="str">
+      <c r="B26" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C26" t="str">
         <v>25-서초구-27</v>
       </c>
-      <c r="D27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E27" t="str">
+      <c r="D26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E26" t="str">
         <v>종균열</v>
       </c>
-      <c r="F27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G27" t="str">
+      <c r="F26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G26" t="str">
         <v>2</v>
       </c>
-      <c r="H27" t="str">
-        <v>-</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="H26" t="str">
+        <v>-</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
         <v>1</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
         <v>1</v>
       </c>
-      <c r="O27" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
+      <c r="O26" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v>서초동 1303-22</v>
       </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str" xml:space="preserve">
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str" xml:space="preserve">
         <v xml:space="preserve">교보타워 주차장 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28">
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27">
         <v>28</v>
       </c>
-      <c r="B28" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C28" t="str">
+      <c r="B27" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C27" t="str">
         <v>25-서초구-28</v>
       </c>
-      <c r="D28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E28" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G28" t="str">
+      <c r="D27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E27" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G27" t="str">
         <v>2</v>
       </c>
-      <c r="H28" t="str">
-        <v>-</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>3</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
-      <c r="O28" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
+      <c r="H27" t="str">
+        <v>-</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v>서초동 1303-35</v>
       </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28" t="str" xml:space="preserve">
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str" xml:space="preserve">
         <v xml:space="preserve">던킹도너츠 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29">
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28">
         <v>29</v>
       </c>
-      <c r="B29" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C29" t="str">
+      <c r="B28" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C28" t="str">
         <v>25-서초구-29</v>
       </c>
-      <c r="D29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E29" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G29" t="str">
+      <c r="D28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E28" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G28" t="str">
         <v>2</v>
       </c>
-      <c r="H29" t="str">
-        <v>-</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>3</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P29" t="str">
-        <v/>
-      </c>
-      <c r="Q29" t="str">
+      <c r="H28" t="str">
+        <v>-</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v>서초동 1304-2</v>
       </c>
-      <c r="R29" t="str">
-        <v/>
-      </c>
-      <c r="S29" t="str" xml:space="preserve">
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str" xml:space="preserve">
         <v xml:space="preserve">수세연 안과의원_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30">
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29">
         <v>30</v>
       </c>
-      <c r="B30" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C30" t="str">
+      <c r="B29" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C29" t="str">
         <v>25-서초구-30</v>
       </c>
-      <c r="D30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E30" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G30" t="str">
+      <c r="D29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E29" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G29" t="str">
         <v>2</v>
       </c>
-      <c r="H30" t="str">
-        <v>-</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>3</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-      <c r="O30" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P30" t="str">
+      <c r="H29" t="str">
+        <v>-</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P29" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="Q29" t="str">
         <v>서초동 1304-3</v>
       </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str" xml:space="preserve">
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str" xml:space="preserve">
         <v xml:space="preserve">자라 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31">
+      <c r="T29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30">
         <v>31</v>
       </c>
-      <c r="B31" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C31" t="str">
+      <c r="B30" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C30" t="str">
         <v>25-서초구-31</v>
       </c>
-      <c r="D31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E31" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G31" t="str">
+      <c r="D30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E30" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G30" t="str">
         <v>2</v>
       </c>
-      <c r="H31" t="str">
-        <v>-</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
-      <c r="O31" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P31" t="str">
+      <c r="H30" t="str">
+        <v>-</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P30" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="Q30" t="str">
         <v>서초동 1305</v>
       </c>
-      <c r="R31" t="str">
-        <v/>
-      </c>
-      <c r="S31" t="str" xml:space="preserve">
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str" xml:space="preserve">
         <v xml:space="preserve">준오헤어 앞_x000d_
 보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32">
+      <c r="T30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31">
         <v>32</v>
       </c>
-      <c r="B32" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C32" t="str">
+      <c r="B31" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C31" t="str">
         <v>25-서초구-32</v>
       </c>
-      <c r="D32" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E32" t="str">
-        <v>-</v>
-      </c>
-      <c r="F32" t="str">
-        <v>-</v>
-      </c>
-      <c r="G32" t="str">
+      <c r="D31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E31" t="str">
+        <v>-</v>
+      </c>
+      <c r="F31" t="str">
+        <v>-</v>
+      </c>
+      <c r="G31" t="str">
         <v>2</v>
       </c>
-      <c r="H32" t="str">
-        <v>-</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P32" t="str">
+      <c r="H31" t="str">
+        <v>-</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P31" t="str">
         <v>보도침하</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="Q31" t="str">
         <v>서초동 1305</v>
       </c>
-      <c r="R32" t="str">
-        <v/>
-      </c>
-      <c r="S32" t="str" xml:space="preserve">
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str" xml:space="preserve">
         <v xml:space="preserve">준오헤어 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33">
+      <c r="T31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32">
         <v>33</v>
       </c>
-      <c r="B33" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C33" t="str">
+      <c r="B32" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C32" t="str">
         <v>25-서초구-33</v>
       </c>
-      <c r="D33" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E33" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F33" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G33" t="str">
+      <c r="D32" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E32" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F32" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G32" t="str">
         <v>2</v>
       </c>
-      <c r="H33" t="str">
-        <v>-</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>3</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>3</v>
-      </c>
-      <c r="O33" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P33" t="str">
-        <v/>
-      </c>
-      <c r="Q33" t="str">
+      <c r="H32" t="str">
+        <v>-</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
         <v>서초동 1305-2</v>
       </c>
-      <c r="R33" t="str">
-        <v/>
-      </c>
-      <c r="S33" t="str" xml:space="preserve">
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str" xml:space="preserve">
         <v xml:space="preserve">라인프렌즈 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34">
+      <c r="T32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33">
         <v>34</v>
       </c>
-      <c r="B34" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C34" t="str">
+      <c r="B33" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C33" t="str">
         <v>25-서초구-34</v>
       </c>
-      <c r="D34" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E34" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F34" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G34" t="str">
+      <c r="D33" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E33" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F33" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G33" t="str">
         <v>2</v>
       </c>
-      <c r="H34" t="str">
-        <v>-</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>3</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>3</v>
-      </c>
-      <c r="O34" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P34" t="str">
-        <v/>
-      </c>
-      <c r="Q34" t="str">
+      <c r="H33" t="str">
+        <v>-</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
         <v>서초동 1305-7</v>
       </c>
-      <c r="R34" t="str">
-        <v/>
-      </c>
-      <c r="S34" t="str" xml:space="preserve">
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str" xml:space="preserve">
         <v xml:space="preserve">올리브영 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35">
+      <c r="T33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
         <v>35</v>
       </c>
-      <c r="B35" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C35" t="str">
+      <c r="B34" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C34" t="str">
         <v>25-서초구-35</v>
       </c>
-      <c r="D35" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E35" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F35" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G35" t="str">
+      <c r="D34" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E34" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F34" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G34" t="str">
         <v>2</v>
       </c>
-      <c r="H35" t="str">
-        <v>-</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>3</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>3</v>
-      </c>
-      <c r="O35" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P35" t="str">
-        <v/>
-      </c>
-      <c r="Q35" t="str">
+      <c r="H34" t="str">
+        <v>-</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
         <v>서초동 1306</v>
       </c>
-      <c r="R35" t="str">
-        <v/>
-      </c>
-      <c r="S35" t="str" xml:space="preserve">
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str" xml:space="preserve">
         <v xml:space="preserve">비엠사오 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36">
+      <c r="T34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35">
         <v>36</v>
       </c>
-      <c r="B36" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C36" t="str">
+      <c r="B35" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C35" t="str">
         <v>25-서초구-36</v>
       </c>
-      <c r="D36" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E36" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F36" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G36" t="str">
+      <c r="D35" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E35" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F35" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G35" t="str">
         <v>2</v>
       </c>
-      <c r="H36" t="str">
-        <v>-</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>3</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P36" t="str">
-        <v/>
-      </c>
-      <c r="Q36" t="str">
+      <c r="H35" t="str">
+        <v>-</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="O35" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
         <v>서초동 1306-2</v>
       </c>
-      <c r="R36" t="str">
-        <v/>
-      </c>
-      <c r="S36" t="str" xml:space="preserve">
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str" xml:space="preserve">
         <v xml:space="preserve">ABC마트 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37">
+      <c r="T35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36">
         <v>37</v>
       </c>
-      <c r="B37" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C37" t="str">
+      <c r="B36" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C36" t="str">
         <v>25-서초구-37</v>
       </c>
-      <c r="D37" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E37" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F37" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G37" t="str">
+      <c r="D36" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E36" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F36" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G36" t="str">
         <v>2</v>
       </c>
-      <c r="H37" t="str">
-        <v>-</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>3</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>3</v>
-      </c>
-      <c r="O37" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P37" t="str">
-        <v/>
-      </c>
-      <c r="Q37" t="str">
+      <c r="H36" t="str">
+        <v>-</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
         <v>서초동 1306-8</v>
       </c>
-      <c r="R37" t="str">
-        <v/>
-      </c>
-      <c r="S37" t="str" xml:space="preserve">
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str" xml:space="preserve">
         <v xml:space="preserve">강남 성모안과 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38">
+      <c r="T36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37">
         <v>38</v>
       </c>
-      <c r="B38" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C38" t="str">
+      <c r="B37" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C37" t="str">
         <v>25-서초구-38</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D37" t="str">
         <v>보통</v>
       </c>
-      <c r="E38" t="str">
-        <v>-</v>
-      </c>
-      <c r="F38" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G38" t="str">
+      <c r="E37" t="str">
+        <v>-</v>
+      </c>
+      <c r="F37" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G37" t="str">
         <v>2</v>
       </c>
-      <c r="H38" t="str">
-        <v>-</v>
-      </c>
-      <c r="I38">
-        <v>3</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>3</v>
-      </c>
-      <c r="O38" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P38" t="str">
+      <c r="H37" t="str">
+        <v>-</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P37" t="str">
         <v>5cm이상 침하</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="Q37" t="str">
         <v>서초동 1306-8</v>
       </c>
-      <c r="R38" t="str">
-        <v/>
-      </c>
-      <c r="S38" t="str" xml:space="preserve">
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str" xml:space="preserve">
         <v xml:space="preserve">강남 성모안과 앞_x000d_
 횡단보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39">
+      <c r="T37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38">
         <v>39</v>
       </c>
-      <c r="B39" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C39" t="str">
+      <c r="B38" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C38" t="str">
         <v>25-서초구-39</v>
       </c>
-      <c r="D39" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E39" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F39" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G39" t="str">
+      <c r="D38" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E38" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F38" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G38" t="str">
         <v>2</v>
       </c>
-      <c r="H39" t="str">
-        <v>-</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>3</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>3</v>
-      </c>
-      <c r="O39" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P39" t="str">
-        <v/>
-      </c>
-      <c r="Q39" t="str">
+      <c r="H38" t="str">
+        <v>-</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
         <v>서초동 1318</v>
       </c>
-      <c r="R39" t="str">
-        <v/>
-      </c>
-      <c r="S39" t="str" xml:space="preserve">
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str" xml:space="preserve">
         <v xml:space="preserve">삼성스토어 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40">
+      <c r="T38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39">
         <v>40</v>
       </c>
-      <c r="B40" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C40" t="str">
+      <c r="B39" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C39" t="str">
         <v>25-서초구-40</v>
       </c>
-      <c r="D40" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E40" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F40" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G40" t="str">
+      <c r="D39" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E39" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F39" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G39" t="str">
         <v>2</v>
       </c>
-      <c r="H40" t="str">
-        <v>-</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>3</v>
-      </c>
-      <c r="O40" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P40" t="str">
+      <c r="H39" t="str">
+        <v>-</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>3</v>
+      </c>
+      <c r="O39" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P39" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q40" t="str">
+      <c r="Q39" t="str">
         <v>서초동 1318-2</v>
       </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str" xml:space="preserve">
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str" xml:space="preserve">
         <v xml:space="preserve">하나은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>26-1</v>
+      </c>
+      <c r="B40" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C40" t="str">
+        <v>26-서초구-01</v>
+      </c>
+      <c r="D40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G40" t="str">
+        <v>3</v>
+      </c>
+      <c r="H40" t="str">
+        <v>-</v>
+      </c>
+      <c r="I40" t="str">
+        <v>0</v>
+      </c>
+      <c r="J40" t="str">
+        <v>0</v>
+      </c>
+      <c r="K40" t="str">
+        <v>0</v>
+      </c>
+      <c r="L40" t="str">
+        <v>0</v>
+      </c>
+      <c r="M40" t="str">
+        <v>0</v>
+      </c>
+      <c r="N40" t="str">
+        <v>0</v>
+      </c>
+      <c r="O40" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P40" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>잠원동12-21</v>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v>꿉당 앞 도로(강남대로615)</v>
+      </c>
       <c r="T40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>26-1</v>
+        <v>26-2</v>
       </c>
       <c r="B41" t="str">
         <v>강남대로</v>
       </c>
       <c r="C41" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
       </c>
       <c r="E41" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F41" t="str">
         <v>양호</v>
@@ -2816,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K41" t="str">
         <v>0</v>
@@ -2828,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O41" t="str">
         <v>일반</v>
@@ -2837,13 +2835,13 @@
         <v>5cm미만 침하</v>
       </c>
       <c r="Q41" t="str">
-        <v>잠원동12-21</v>
+        <v>잠원동12-22</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>꿉당 앞 도로(강남대로615)</v>
+        <v>성락빌딩 앞 횡단보도(강남대로613)</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2851,19 +2849,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-2</v>
+        <v>26-3</v>
       </c>
       <c r="B42" t="str">
         <v>강남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F42" t="str">
         <v>양호</v>
@@ -2878,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" t="str">
         <v>0</v>
@@ -2890,22 +2888,22 @@
         <v>0</v>
       </c>
       <c r="N42" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q42" t="str">
-        <v>잠원동12-22</v>
+        <v>잠원동13-6</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>성락빌딩 앞 횡단보도(강남대로613)</v>
+        <v>GS칼텍스 직역 남서울주유소 앞 교차로(나루터로83)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2913,19 +2911,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-3</v>
+        <v>26-4</v>
       </c>
       <c r="B43" t="str">
         <v>강남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>종,횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F43" t="str">
         <v>양호</v>
@@ -2940,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" t="str">
         <v>0</v>
@@ -2952,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
@@ -2961,13 +2959,13 @@
         <v>-</v>
       </c>
       <c r="Q43" t="str">
-        <v>잠원동13-6</v>
+        <v>잠원동20-9</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>GS칼텍스 직역 남서울주유소 앞 교차로(나루터로83)</v>
+        <v>휴먼타워 앞 신사역 교차로(강남대로605)</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2975,19 +2973,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-4</v>
+        <v>26-5</v>
       </c>
       <c r="B44" t="str">
         <v>강남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F44" t="str">
         <v>양호</v>
@@ -3002,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" t="str">
         <v>0</v>
@@ -3014,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
@@ -3023,13 +3021,13 @@
         <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>잠원동20-9</v>
+        <v>잠원동20-5</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>휴먼타워 앞 신사역 교차로(강남대로605)</v>
+        <v>인성빌딩 파리바게트 앞 횡단보도(강남대로603)</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -3037,19 +3035,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-5</v>
+        <v>26-6</v>
       </c>
       <c r="B45" t="str">
         <v>강남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -3064,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="str">
         <v>0</v>
@@ -3076,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
@@ -3085,13 +3083,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>잠원동20-5</v>
+        <v>잠원동21-3</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>인성빌딩 파리바게트 앞 횡단보도(강남대로603)</v>
+        <v>진미선빌딩 앞 도로(강남대로597)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3099,19 +3097,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-6</v>
+        <v>26-7</v>
       </c>
       <c r="B46" t="str">
         <v>강남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3126,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="str">
         <v>0</v>
@@ -3144,7 +3142,7 @@
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q46" t="str">
         <v>잠원동21-3</v>
@@ -3153,7 +3151,7 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>진미선빌딩 앞 도로(강남대로597)</v>
+        <v>버스전용차선(강남대로597)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3161,19 +3159,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-7</v>
+        <v>26-8</v>
       </c>
       <c r="B47" t="str">
         <v>강남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>양호</v>
+        <v>거북동</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3188,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3200,22 +3198,22 @@
         <v>0</v>
       </c>
       <c r="N47" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>잠원동21-3</v>
+        <v>잠원동27-2</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>버스전용차선(강남대로597)</v>
+        <v>메디칼타워 올리브영 앞 도로(강남대로589)</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3223,19 +3221,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-8</v>
+        <v>26-9</v>
       </c>
       <c r="B48" t="str">
         <v>강남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>거북동</v>
+        <v>거북등</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3268,16 +3266,16 @@
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q48" t="str">
-        <v>잠원동27-2</v>
+        <v>잠원동27-8</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>메디칼타워 올리브영 앞 도로(강남대로589)</v>
+        <v>KCC건설 앞 도로(강남대로587)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3285,13 +3283,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-9</v>
+        <v>26-10</v>
       </c>
       <c r="B49" t="str">
         <v>강남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3330,16 +3328,16 @@
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q49" t="str">
-        <v>잠원동27-8</v>
+        <v>잠원동28-10</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>KCC건설 앞 도로(강남대로587)</v>
+        <v>HY빌딩 앞 도로(강남대로577)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3347,13 +3345,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B50" t="str">
         <v>강남대로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3395,13 +3393,13 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>잠원동28-10</v>
+        <v>잠원동28-6</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>HY빌딩 앞 도로(강남대로577)</v>
+        <v>인접공사현장 앞 도로(강남대로573)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3409,13 +3407,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B51" t="str">
         <v>강남대로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3457,13 +3455,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>잠원동28-6</v>
+        <v>잠원동36-13</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>인접공사현장 앞 도로(강남대로573)</v>
+        <v>더뉴치과의원 앞 도로(강남대로567)</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3471,19 +3469,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B52" t="str">
         <v>강남대로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
       </c>
       <c r="E52" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F52" t="str">
         <v>양호</v>
@@ -3498,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" t="str">
         <v>0</v>
@@ -3510,13 +3508,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="str">
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q52" t="str">
         <v>잠원동36-13</v>
@@ -3525,7 +3523,7 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>더뉴치과의원 앞 도로(강남대로567)</v>
+        <v>버스전용차선 (강남대로567)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3533,19 +3531,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B53" t="str">
         <v>강남대로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
       </c>
       <c r="E53" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F53" t="str">
         <v>양호</v>
@@ -3560,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53" t="str">
         <v>0</v>
@@ -3572,22 +3570,22 @@
         <v>0</v>
       </c>
       <c r="N53" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O53" t="str">
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>잠원동36-13</v>
+        <v>잠원동37-6</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>버스전용차선 (강남대로567)</v>
+        <v>정인빌딩 광주은행 앞 도로(강남대로559)</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3595,13 +3593,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B54" t="str">
         <v>강남대로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3640,16 +3638,16 @@
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q54" t="str">
-        <v>잠원동37-6</v>
+        <v>논현역교차로</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>정인빌딩 광주은행 앞 도로(강남대로559)</v>
+        <v>논현역 교차로(학동로102)</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3657,13 +3655,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B55" t="str">
         <v>강남대로</v>
       </c>
       <c r="C55" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3702,16 +3700,16 @@
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q55" t="str">
-        <v>논현역교차로</v>
+        <v>반포동706-10</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>논현역 교차로(학동로102)</v>
+        <v>논현역 #5출구 앞 횡단보도(강남대로545-4)</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3719,13 +3717,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B56" t="str">
         <v>강남대로</v>
       </c>
       <c r="C56" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3767,13 +3765,13 @@
         <v>-</v>
       </c>
       <c r="Q56" t="str">
-        <v>반포동706-10</v>
+        <v>반포동707-11</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>논현역 #5출구 앞 횡단보도(강남대로545-4)</v>
+        <v>프린스빌딩 서브웨이 앞(강남대로535)</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3781,13 +3779,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B57" t="str">
         <v>강남대로</v>
       </c>
       <c r="C57" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3829,13 +3827,13 @@
         <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>반포동707-11</v>
+        <v>반포동722-20</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>프린스빌딩 서브웨이 앞(강남대로535)</v>
+        <v>브랜드칸타워 투썸플레이스 앞(강남대로527)</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3843,13 +3841,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B58" t="str">
         <v>강남대로</v>
       </c>
       <c r="C58" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3891,27 +3889,27 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>반포동722-20</v>
+        <v>반포동722-31</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>브랜드칸타워 투썸플레이스 앞(강남대로527)</v>
+        <v>성창빌딩 메가커피 앞 횡단보도(강남대로523)</v>
       </c>
       <c r="T58" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B59" t="str">
         <v>강남대로</v>
       </c>
       <c r="C59" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3950,30 +3948,30 @@
         <v>일반</v>
       </c>
       <c r="P59" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q59" t="str">
-        <v>반포동722-31</v>
+        <v>반포동722-38</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>성창빌딩 메가커피 앞 횡단보도(강남대로523)</v>
+        <v>태영빌딩 올리브약국 앞(강남대로521-4)</v>
       </c>
       <c r="T59" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B60" t="str">
         <v>강남대로</v>
       </c>
       <c r="C60" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -4012,30 +4010,30 @@
         <v>일반</v>
       </c>
       <c r="P60" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q60" t="str">
-        <v>반포동722-38</v>
+        <v>반포동723-22</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>태영빌딩 올리브약국 앞(강남대로521-4)</v>
+        <v>하늘안과 앞 (강남대로509)</v>
       </c>
       <c r="T60" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B61" t="str">
         <v>강남대로</v>
       </c>
       <c r="C61" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4077,27 +4075,27 @@
         <v>-</v>
       </c>
       <c r="Q61" t="str">
-        <v>반포동723-22</v>
+        <v>반포동736-17</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>하늘안과 앞 (강남대로509)</v>
+        <v>청하빌딩 커피빈 앞(강남대로503)</v>
       </c>
       <c r="T61" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B62" t="str">
         <v>강남대로</v>
       </c>
       <c r="C62" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4139,27 +4137,27 @@
         <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>반포동736-17</v>
+        <v>반포동737-19</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>청하빌딩 커피빈 앞(강남대로503)</v>
+        <v>철거현장(강남대로79길2)</v>
       </c>
       <c r="T62" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B63" t="str">
         <v>강남대로</v>
       </c>
       <c r="C63" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4201,27 +4199,27 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>반포동737-19</v>
+        <v>반포동748-6</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>철거현장(강남대로79길2)</v>
+        <v>페이지랩의원 앞(강남대로477)</v>
       </c>
       <c r="T63" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B64" t="str">
         <v>강남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4263,27 +4261,27 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>반포동748-6</v>
+        <v>교보타워사거리</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>페이지랩의원 앞(강남대로477)</v>
+        <v>신논현역 교차로 횡단보도(봉은사로102)</v>
       </c>
       <c r="T64" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B65" t="str">
         <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4322,30 +4320,30 @@
         <v>일반</v>
       </c>
       <c r="P65" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q65" t="str">
-        <v>교보타워사거리</v>
+        <v>서초동1303-37</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>신논현역 교차로 횡단보도(봉은사로102)</v>
+        <v>w타워 하이디라오 앞(서초대로77길54)</v>
       </c>
       <c r="T65" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-26</v>
+        <v>26-27</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-26</v>
+        <v>26-서초구-27</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4387,21 +4385,331 @@
         <v>5cm미만 침하</v>
       </c>
       <c r="Q66" t="str">
-        <v>서초동1303-37</v>
+        <v>서초동1304-3</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>w타워 하이디라오 앞(서초대로77길54)</v>
+        <v>남서울빌딩 자라 앞도로(강남대로447)</v>
       </c>
       <c r="T66" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>26-28</v>
+      </c>
+      <c r="B67" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C67" t="str">
+        <v>26-서초구-28</v>
+      </c>
+      <c r="D67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E67" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G67" t="str">
+        <v>3</v>
+      </c>
+      <c r="H67" t="str">
+        <v>-</v>
+      </c>
+      <c r="I67" t="str">
+        <v>0</v>
+      </c>
+      <c r="J67" t="str">
+        <v>3</v>
+      </c>
+      <c r="K67" t="str">
+        <v>0</v>
+      </c>
+      <c r="L67" t="str">
+        <v>0</v>
+      </c>
+      <c r="M67" t="str">
+        <v>0</v>
+      </c>
+      <c r="N67" t="str">
+        <v>3</v>
+      </c>
+      <c r="O67" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P67" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>서초동1305-2</v>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v>유화빌딩 미앤미의원_강남 앞도로(강남대로439)</v>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>26-29</v>
+      </c>
+      <c r="B68" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C68" t="str">
+        <v>26-서초구-29</v>
+      </c>
+      <c r="D68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E68" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G68" t="str">
+        <v>3</v>
+      </c>
+      <c r="H68" t="str">
+        <v>-</v>
+      </c>
+      <c r="I68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J68" t="str">
+        <v>3</v>
+      </c>
+      <c r="K68" t="str">
+        <v>0</v>
+      </c>
+      <c r="L68" t="str">
+        <v>0</v>
+      </c>
+      <c r="M68" t="str">
+        <v>0</v>
+      </c>
+      <c r="N68" t="str">
+        <v>3</v>
+      </c>
+      <c r="O68" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P68" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>서초동1305-7</v>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v>동일빌딩 뽀송의원_강남 앞도로(강남대로429)</v>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>26-30</v>
+      </c>
+      <c r="B69" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C69" t="str">
+        <v>26-서초구-30</v>
+      </c>
+      <c r="D69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G69" t="str">
+        <v>3</v>
+      </c>
+      <c r="H69" t="str">
+        <v>-</v>
+      </c>
+      <c r="I69" t="str">
+        <v>0</v>
+      </c>
+      <c r="J69" t="str">
+        <v>0</v>
+      </c>
+      <c r="K69" t="str">
+        <v>0</v>
+      </c>
+      <c r="L69" t="str">
+        <v>0</v>
+      </c>
+      <c r="M69" t="str">
+        <v>0</v>
+      </c>
+      <c r="N69" t="str">
+        <v>0</v>
+      </c>
+      <c r="O69" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P69" t="str">
+        <v>5cm미만 침하</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>서초동1306-8</v>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v>대동빌딩 우리은행 앞 도로(강남대로415)</v>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>26-31</v>
+      </c>
+      <c r="B70" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C70" t="str">
+        <v>26-서초구-31</v>
+      </c>
+      <c r="D70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E70" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G70" t="str">
+        <v>3</v>
+      </c>
+      <c r="H70" t="str">
+        <v>-</v>
+      </c>
+      <c r="I70" t="str">
+        <v>0</v>
+      </c>
+      <c r="J70" t="str">
+        <v>3</v>
+      </c>
+      <c r="K70" t="str">
+        <v>0</v>
+      </c>
+      <c r="L70" t="str">
+        <v>0</v>
+      </c>
+      <c r="M70" t="str">
+        <v>0</v>
+      </c>
+      <c r="N70" t="str">
+        <v>3</v>
+      </c>
+      <c r="O70" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P70" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>서초동1318</v>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v>삼성스토어 앞 도로(강남대로411)</v>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>26-32</v>
+      </c>
+      <c r="B71" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C71" t="str">
+        <v>26-서초구-32</v>
+      </c>
+      <c r="D71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E71" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G71" t="str">
+        <v>3</v>
+      </c>
+      <c r="H71" t="str">
+        <v>-</v>
+      </c>
+      <c r="I71" t="str">
+        <v>0</v>
+      </c>
+      <c r="J71" t="str">
+        <v>3</v>
+      </c>
+      <c r="K71" t="str">
+        <v>0</v>
+      </c>
+      <c r="L71" t="str">
+        <v>0</v>
+      </c>
+      <c r="M71" t="str">
+        <v>0</v>
+      </c>
+      <c r="N71" t="str">
+        <v>3</v>
+      </c>
+      <c r="O71" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P71" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>서초동1318-2</v>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v>통영빌딩 하나은행 앞 도로(강남대로405)</v>
+      </c>
+      <c r="T71" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
   </ignoredErrors>
 </worksheet>
 </file>